--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChaeSeunghyeon\Desktop\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2FC609-B8F0-4F15-9051-4C47F1E863AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7077651-0277-4E94-A3E1-A5BC337BD518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
   </bookViews>
@@ -60,10 +60,6 @@
   </si>
   <si>
     <t>intelligence</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dexteritry</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -188,6 +184,10 @@
   </si>
   <si>
     <t>stacked_exp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dexterity</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,30 +640,30 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -678,16 +678,16 @@
         <v>4</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -721,7 +721,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -861,7 +861,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -8783,7 +8783,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -11473,21 +11473,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -11503,7 +11503,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -11520,7 +11520,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -11528,7 +11528,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -11536,7 +11536,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -11544,7 +11544,7 @@
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -11552,7 +11552,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -11560,12 +11560,12 @@
         <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -11573,7 +11573,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -11581,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -11589,7 +11589,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -11597,7 +11597,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -11605,12 +11605,12 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -11618,7 +11618,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -11626,7 +11626,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -11634,7 +11634,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -11642,7 +11642,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -11650,12 +11650,12 @@
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -11663,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -11671,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -11679,7 +11679,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -11687,7 +11687,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -11695,7 +11695,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7077651-0277-4E94-A3E1-A5BC337BD518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6099CBCA-7E63-4FBC-9240-3C53D0AF84E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
   </bookViews>
@@ -155,22 +155,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>THIEF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAGICION</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASCETIC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,6 +172,22 @@
   </si>
   <si>
     <t>dexterity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROGUE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NONE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +640,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
@@ -652,7 +652,7 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>9</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -3439,7 +3439,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -8783,7 +8783,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -11487,7 +11487,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -11503,7 +11503,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -11565,7 +11565,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -11610,7 +11610,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -11655,7 +11655,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">

--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6099CBCA-7E63-4FBC-9240-3C53D0AF84E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92D5278-B3C3-418A-8C58-6C30850A98E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
   </bookViews>
   <sheets>
     <sheet name="ability" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>진검</t>
   </si>
   <si>
-    <t>귀객</t>
-  </si>
-  <si>
     <t>태성</t>
   </si>
   <si>
@@ -188,6 +185,10 @@
   </si>
   <si>
     <t>NONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>귀검</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -640,7 +641,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
@@ -652,7 +653,7 @@
         <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>9</v>
@@ -663,7 +664,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
@@ -721,7 +722,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -861,7 +862,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3439,7 +3440,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -6110,7 +6111,7 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -8783,7 +8784,7 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -11476,18 +11477,18 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -11503,7 +11504,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -11512,7 +11513,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -11520,7 +11521,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -11565,7 +11566,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -11597,7 +11598,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -11605,12 +11606,12 @@
         <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -11618,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -11626,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
@@ -11634,7 +11635,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -11642,7 +11643,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -11650,12 +11651,12 @@
         <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -11663,7 +11664,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -11671,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
@@ -11679,7 +11680,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -11687,7 +11688,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.3">
@@ -11695,7 +11696,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/class.xlsx
+++ b/resources/table/class.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92D5278-B3C3-418A-8C58-6C30850A98E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11707E9E-9E75-4851-89D3-DEA67C952299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{51E714AE-D231-4317-A66B-833316D0EFD8}"/>
   </bookViews>
   <sheets>
     <sheet name="ability" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,10 +161,6 @@
   </si>
   <si>
     <t>평민</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>stacked_exp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -619,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0974CDB6-B042-4597-8135-F5DEE2EA35B3}">
-  <dimension ref="A1:I393"/>
+  <dimension ref="A1:H393"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.25" style="3" bestFit="1" customWidth="1"/>
@@ -628,12 +624,11 @@
     <col min="4" max="4" width="9.875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.75" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="3"/>
+    <col min="7" max="8" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -641,7 +636,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>5</v>
@@ -652,17 +647,14 @@
       <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>36</v>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>31</v>
       </c>
@@ -687,11 +679,8 @@
       <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -716,16 +705,13 @@
       <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="6">
         <v>1</v>
       </c>
@@ -742,17 +728,13 @@
         <v>300</v>
       </c>
       <c r="G5" s="6">
-        <f>SUM(G4,F5)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H5" s="6">
         <v>0</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="6">
         <v>2</v>
       </c>
@@ -769,17 +751,13 @@
         <v>300</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" ref="G6:G9" si="0">SUM(G5,F6)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H6" s="6">
         <v>0</v>
       </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6">
         <v>3</v>
       </c>
@@ -796,17 +774,13 @@
         <v>300</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6">
         <v>0</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="6">
         <v>4</v>
       </c>
@@ -823,17 +797,13 @@
         <v>300</v>
       </c>
       <c r="G8" s="6">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6">
         <v>0</v>
       </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="6">
         <v>5</v>
       </c>
@@ -850,17 +820,13 @@
         <v>0</v>
       </c>
       <c r="G9" s="6">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6">
         <v>0</v>
       </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
@@ -871,9 +837,8 @@
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="6">
         <v>5</v>
       </c>
@@ -890,17 +855,13 @@
         <v>1200</v>
       </c>
       <c r="G11" s="6">
-        <f>SUM(G9,F11)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="6">
         <v>6</v>
       </c>
@@ -917,17 +878,13 @@
         <v>1200</v>
       </c>
       <c r="G12" s="6">
-        <f>SUM(G11,F12)</f>
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6">
         <v>0</v>
       </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="6">
         <v>7</v>
       </c>
@@ -944,17 +901,13 @@
         <v>1200</v>
       </c>
       <c r="G13" s="6">
-        <f t="shared" ref="G13:G76" si="1">SUM(G12,F13)</f>
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="H13" s="6">
         <v>0</v>
       </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="6">
         <v>8</v>
       </c>
@@ -971,17 +924,13 @@
         <v>1200</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6">
         <v>0</v>
       </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="6">
         <v>9</v>
       </c>
@@ -998,17 +947,13 @@
         <v>2400</v>
       </c>
       <c r="G15" s="6">
-        <f t="shared" si="1"/>
-        <v>8400</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6">
         <v>0</v>
       </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="6">
         <v>10</v>
       </c>
@@ -1025,17 +970,13 @@
         <v>2400</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="1"/>
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6">
         <v>0</v>
       </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="6">
         <v>11</v>
       </c>
@@ -1052,17 +993,13 @@
         <v>2400</v>
       </c>
       <c r="G17" s="6">
-        <f t="shared" si="1"/>
-        <v>13200</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6">
         <v>0</v>
       </c>
-      <c r="I17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="6">
         <v>12</v>
       </c>
@@ -1079,17 +1016,13 @@
         <v>4800</v>
       </c>
       <c r="G18" s="6">
-        <f t="shared" si="1"/>
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="H18" s="6">
         <v>0</v>
       </c>
-      <c r="I18" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="6">
         <v>13</v>
       </c>
@@ -1106,17 +1039,13 @@
         <v>4800</v>
       </c>
       <c r="G19" s="6">
-        <f t="shared" si="1"/>
-        <v>22800</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6">
         <v>0</v>
       </c>
-      <c r="I19" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="6">
         <v>14</v>
       </c>
@@ -1133,17 +1062,13 @@
         <v>4800</v>
       </c>
       <c r="G20" s="6">
-        <f t="shared" si="1"/>
-        <v>27600</v>
+        <v>0</v>
       </c>
       <c r="H20" s="6">
         <v>0</v>
       </c>
-      <c r="I20" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="6">
         <v>15</v>
       </c>
@@ -1160,17 +1085,13 @@
         <v>4800</v>
       </c>
       <c r="G21" s="6">
-        <f t="shared" si="1"/>
-        <v>32400</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6">
         <v>0</v>
       </c>
-      <c r="I21" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="6">
         <v>16</v>
       </c>
@@ -1187,17 +1108,13 @@
         <v>9600</v>
       </c>
       <c r="G22" s="6">
-        <f t="shared" si="1"/>
-        <v>42000</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6">
         <v>0</v>
       </c>
-      <c r="I22" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="6">
         <v>17</v>
       </c>
@@ -1214,17 +1131,13 @@
         <v>9600</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="1"/>
-        <v>51600</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6">
         <v>0</v>
       </c>
-      <c r="I23" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="6">
         <v>18</v>
       </c>
@@ -1241,17 +1154,13 @@
         <v>19200</v>
       </c>
       <c r="G24" s="6">
-        <f t="shared" si="1"/>
-        <v>70800</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6">
         <v>0</v>
       </c>
-      <c r="I24" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="6">
         <v>19</v>
       </c>
@@ -1268,17 +1177,13 @@
         <v>19200</v>
       </c>
       <c r="G25" s="6">
-        <f t="shared" si="1"/>
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6">
         <v>0</v>
       </c>
-      <c r="I25" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="6">
         <v>20</v>
       </c>
@@ -1295,17 +1200,13 @@
         <v>19200</v>
       </c>
       <c r="G26" s="6">
-        <f t="shared" si="1"/>
-        <v>109200</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6">
         <v>0</v>
       </c>
-      <c r="I26" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="6">
         <v>21</v>
       </c>
@@ -1322,17 +1223,13 @@
         <v>38400</v>
       </c>
       <c r="G27" s="6">
-        <f t="shared" si="1"/>
-        <v>147600</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6">
         <v>0</v>
       </c>
-      <c r="I27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="6">
         <v>22</v>
       </c>
@@ -1349,17 +1246,13 @@
         <v>38400</v>
       </c>
       <c r="G28" s="6">
-        <f t="shared" si="1"/>
-        <v>186000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6">
         <v>0</v>
       </c>
-      <c r="I28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="6">
         <v>23</v>
       </c>
@@ -1376,17 +1269,13 @@
         <v>38400</v>
       </c>
       <c r="G29" s="6">
-        <f t="shared" si="1"/>
-        <v>224400</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6">
         <v>0</v>
       </c>
-      <c r="I29" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B30" s="6">
         <v>24</v>
       </c>
@@ -1403,17 +1292,13 @@
         <v>38400</v>
       </c>
       <c r="G30" s="6">
-        <f t="shared" si="1"/>
-        <v>262800</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6">
         <v>0</v>
       </c>
-      <c r="I30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B31" s="6">
         <v>25</v>
       </c>
@@ -1430,17 +1315,13 @@
         <v>76800</v>
       </c>
       <c r="G31" s="6">
-        <f t="shared" si="1"/>
-        <v>339600</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6">
         <v>0</v>
       </c>
-      <c r="I31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B32" s="6">
         <v>26</v>
       </c>
@@ -1457,17 +1338,13 @@
         <v>76800</v>
       </c>
       <c r="G32" s="6">
-        <f t="shared" si="1"/>
-        <v>416400</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6">
         <v>0</v>
       </c>
-      <c r="I32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="6">
         <v>27</v>
       </c>
@@ -1484,17 +1361,13 @@
         <v>76800</v>
       </c>
       <c r="G33" s="6">
-        <f t="shared" si="1"/>
-        <v>493200</v>
+        <v>0</v>
       </c>
       <c r="H33" s="6">
         <v>0</v>
       </c>
-      <c r="I33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="6">
         <v>28</v>
       </c>
@@ -1511,17 +1384,13 @@
         <v>153600</v>
       </c>
       <c r="G34" s="6">
-        <f t="shared" si="1"/>
-        <v>646800</v>
+        <v>0</v>
       </c>
       <c r="H34" s="6">
         <v>0</v>
       </c>
-      <c r="I34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="6">
         <v>29</v>
       </c>
@@ -1538,17 +1407,13 @@
         <v>142600</v>
       </c>
       <c r="G35" s="6">
-        <f t="shared" si="1"/>
-        <v>789400</v>
+        <v>0</v>
       </c>
       <c r="H35" s="6">
         <v>0</v>
       </c>
-      <c r="I35" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="6">
         <v>30</v>
       </c>
@@ -1565,17 +1430,13 @@
         <v>153600</v>
       </c>
       <c r="G36" s="6">
-        <f t="shared" si="1"/>
-        <v>943000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="6">
         <v>0</v>
       </c>
-      <c r="I36" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="6">
         <v>31</v>
       </c>
@@ -1592,17 +1453,13 @@
         <v>225000</v>
       </c>
       <c r="G37" s="6">
-        <f t="shared" si="1"/>
-        <v>1168000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6">
         <v>0</v>
       </c>
-      <c r="I37" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="6">
         <v>32</v>
       </c>
@@ -1619,17 +1476,13 @@
         <v>225000</v>
       </c>
       <c r="G38" s="6">
-        <f t="shared" si="1"/>
-        <v>1393000</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6">
         <v>0</v>
       </c>
-      <c r="I38" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="6">
         <v>33</v>
       </c>
@@ -1646,17 +1499,13 @@
         <v>225000</v>
       </c>
       <c r="G39" s="6">
-        <f t="shared" si="1"/>
-        <v>1618000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6">
         <v>0</v>
       </c>
-      <c r="I39" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="6">
         <v>34</v>
       </c>
@@ -1673,17 +1522,13 @@
         <v>312600</v>
       </c>
       <c r="G40" s="6">
-        <f t="shared" si="1"/>
-        <v>1930600</v>
+        <v>0</v>
       </c>
       <c r="H40" s="6">
         <v>0</v>
       </c>
-      <c r="I40" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="6">
         <v>35</v>
       </c>
@@ -1700,17 +1545,13 @@
         <v>384000</v>
       </c>
       <c r="G41" s="6">
-        <f t="shared" si="1"/>
-        <v>2314600</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6">
         <v>0</v>
       </c>
-      <c r="I41" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="6">
         <v>36</v>
       </c>
@@ -1727,17 +1568,13 @@
         <v>225000</v>
       </c>
       <c r="G42" s="6">
-        <f t="shared" si="1"/>
-        <v>2539600</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6">
         <v>0</v>
       </c>
-      <c r="I42" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="6">
         <v>37</v>
       </c>
@@ -1754,17 +1591,13 @@
         <v>450000</v>
       </c>
       <c r="G43" s="6">
-        <f t="shared" si="1"/>
-        <v>2989600</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6">
         <v>0</v>
       </c>
-      <c r="I43" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="6">
         <v>38</v>
       </c>
@@ -1781,17 +1614,13 @@
         <v>450000</v>
       </c>
       <c r="G44" s="6">
-        <f t="shared" si="1"/>
-        <v>3439600</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6">
         <v>0</v>
       </c>
-      <c r="I44" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="6">
         <v>39</v>
       </c>
@@ -1808,17 +1637,13 @@
         <v>450000</v>
       </c>
       <c r="G45" s="6">
-        <f t="shared" si="1"/>
-        <v>3889600</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6">
         <v>0</v>
       </c>
-      <c r="I45" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="6">
         <v>40</v>
       </c>
@@ -1835,17 +1660,13 @@
         <v>491520</v>
       </c>
       <c r="G46" s="6">
-        <f t="shared" si="1"/>
-        <v>4381120</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6">
         <v>0</v>
       </c>
-      <c r="I46" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="6">
         <v>41</v>
       </c>
@@ -1862,17 +1683,13 @@
         <v>491520</v>
       </c>
       <c r="G47" s="6">
-        <f t="shared" si="1"/>
-        <v>4872640</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6">
         <v>0</v>
       </c>
-      <c r="I47" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="6">
         <v>42</v>
       </c>
@@ -1889,17 +1706,13 @@
         <v>491520</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="1"/>
-        <v>5364160</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6">
         <v>0</v>
       </c>
-      <c r="I48" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="6">
         <v>43</v>
       </c>
@@ -1916,17 +1729,13 @@
         <v>720000</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="1"/>
-        <v>6084160</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6">
         <v>0</v>
       </c>
-      <c r="I49" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="6">
         <v>44</v>
       </c>
@@ -1943,17 +1752,13 @@
         <v>720000</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="1"/>
-        <v>6804160</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6">
         <v>0</v>
       </c>
-      <c r="I50" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="6">
         <v>45</v>
       </c>
@@ -1970,17 +1775,13 @@
         <v>983040</v>
       </c>
       <c r="G51" s="6">
-        <f t="shared" si="1"/>
-        <v>7787200</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6">
         <v>0</v>
       </c>
-      <c r="I51" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="6">
         <v>46</v>
       </c>
@@ -1997,17 +1798,13 @@
         <v>983040</v>
       </c>
       <c r="G52" s="6">
-        <f t="shared" si="1"/>
-        <v>8770240</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6">
         <v>0</v>
       </c>
-      <c r="I52" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="6">
         <v>47</v>
       </c>
@@ -2024,17 +1821,13 @@
         <v>983040</v>
       </c>
       <c r="G53" s="6">
-        <f t="shared" si="1"/>
-        <v>9753280</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6">
         <v>0</v>
       </c>
-      <c r="I53" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="6">
         <v>48</v>
       </c>
@@ -2051,17 +1844,13 @@
         <v>1440000</v>
       </c>
       <c r="G54" s="6">
-        <f t="shared" si="1"/>
-        <v>11193280</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6">
         <v>0</v>
       </c>
-      <c r="I54" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="6">
         <v>49</v>
       </c>
@@ -2078,17 +1867,13 @@
         <v>1440000</v>
       </c>
       <c r="G55" s="6">
-        <f t="shared" si="1"/>
-        <v>12633280</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6">
         <v>0</v>
       </c>
-      <c r="I55" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="6">
         <v>50</v>
       </c>
@@ -2105,17 +1890,13 @@
         <v>1440000</v>
       </c>
       <c r="G56" s="6">
-        <f t="shared" si="1"/>
-        <v>14073280</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6">
         <v>0</v>
       </c>
-      <c r="I56" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="6">
         <v>51</v>
       </c>
@@ -2132,17 +1913,13 @@
         <v>1630000</v>
       </c>
       <c r="G57" s="6">
-        <f t="shared" si="1"/>
-        <v>15703280</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6">
         <v>0</v>
       </c>
-      <c r="I57" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="6">
         <v>52</v>
       </c>
@@ -2159,17 +1936,13 @@
         <v>1630000</v>
       </c>
       <c r="G58" s="6">
-        <f t="shared" si="1"/>
-        <v>17333280</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6">
         <v>0</v>
       </c>
-      <c r="I58" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="6">
         <v>53</v>
       </c>
@@ -2186,17 +1959,13 @@
         <v>1630000</v>
       </c>
       <c r="G59" s="6">
-        <f t="shared" si="1"/>
-        <v>18963280</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6">
         <v>0</v>
       </c>
-      <c r="I59" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="6">
         <v>54</v>
       </c>
@@ -2213,17 +1982,13 @@
         <v>2400000</v>
       </c>
       <c r="G60" s="6">
-        <f t="shared" si="1"/>
-        <v>21363280</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6">
         <v>0</v>
       </c>
-      <c r="I60" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="6">
         <v>55</v>
       </c>
@@ -2240,17 +2005,13 @@
         <v>2400000</v>
       </c>
       <c r="G61" s="6">
-        <f t="shared" si="1"/>
-        <v>23763280</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6">
         <v>0</v>
       </c>
-      <c r="I61" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="6">
         <v>56</v>
       </c>
@@ -2267,17 +2028,13 @@
         <v>2400000</v>
       </c>
       <c r="G62" s="6">
-        <f t="shared" si="1"/>
-        <v>26163280</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6">
         <v>0</v>
       </c>
-      <c r="I62" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="6">
         <v>57</v>
       </c>
@@ -2294,17 +2051,13 @@
         <v>3500000</v>
       </c>
       <c r="G63" s="6">
-        <f t="shared" si="1"/>
-        <v>29663280</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6">
         <v>0</v>
       </c>
-      <c r="I63" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="6">
         <v>58</v>
       </c>
@@ -2321,17 +2074,13 @@
         <v>5500000</v>
       </c>
       <c r="G64" s="6">
-        <f t="shared" si="1"/>
-        <v>35163280</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6">
         <v>0</v>
       </c>
-      <c r="I64" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="6">
         <v>59</v>
       </c>
@@ -2348,17 +2097,13 @@
         <v>4500000</v>
       </c>
       <c r="G65" s="6">
-        <f t="shared" si="1"/>
-        <v>39663280</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6">
         <v>0</v>
       </c>
-      <c r="I65" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="6">
         <v>60</v>
       </c>
@@ -2375,17 +2120,13 @@
         <v>7400000</v>
       </c>
       <c r="G66" s="6">
-        <f t="shared" si="1"/>
-        <v>47063280</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6">
         <v>0</v>
       </c>
-      <c r="I66" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="6">
         <v>61</v>
       </c>
@@ -2402,17 +2143,13 @@
         <v>7400000</v>
       </c>
       <c r="G67" s="6">
-        <f t="shared" si="1"/>
-        <v>54463280</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6">
         <v>0</v>
       </c>
-      <c r="I67" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="6">
         <v>62</v>
       </c>
@@ -2429,17 +2166,13 @@
         <v>8400000</v>
       </c>
       <c r="G68" s="6">
-        <f t="shared" si="1"/>
-        <v>62863280</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6">
         <v>0</v>
       </c>
-      <c r="I68" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="6">
         <v>63</v>
       </c>
@@ -2456,17 +2189,13 @@
         <v>9320000</v>
       </c>
       <c r="G69" s="6">
-        <f t="shared" si="1"/>
-        <v>72183280</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
         <v>0</v>
       </c>
-      <c r="I69" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="6">
         <v>64</v>
       </c>
@@ -2483,17 +2212,13 @@
         <v>8320000</v>
       </c>
       <c r="G70" s="6">
-        <f t="shared" si="1"/>
-        <v>80503280</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6">
         <v>0</v>
       </c>
-      <c r="I70" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="6">
         <v>65</v>
       </c>
@@ -2510,17 +2235,13 @@
         <v>9320000</v>
       </c>
       <c r="G71" s="6">
-        <f t="shared" si="1"/>
-        <v>89823280</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6">
         <v>0</v>
       </c>
-      <c r="I71" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="6">
         <v>66</v>
       </c>
@@ -2537,17 +2258,13 @@
         <v>10450000</v>
       </c>
       <c r="G72" s="6">
-        <f t="shared" si="1"/>
-        <v>100273280</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6">
         <v>0</v>
       </c>
-      <c r="I72" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="6">
         <v>67</v>
       </c>
@@ -2564,17 +2281,13 @@
         <v>11000000</v>
       </c>
       <c r="G73" s="6">
-        <f t="shared" si="1"/>
-        <v>111273280</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6">
         <v>0</v>
       </c>
-      <c r="I73" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="6">
         <v>68</v>
       </c>
@@ -2591,17 +2304,13 @@
         <v>13000000</v>
       </c>
       <c r="G74" s="6">
-        <f t="shared" si="1"/>
-        <v>124273280</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6">
         <v>0</v>
       </c>
-      <c r="I74" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="6">
         <v>69</v>
       </c>
@@ -2618,17 +2327,13 @@
         <v>15000000</v>
       </c>
       <c r="G75" s="6">
-        <f t="shared" si="1"/>
-        <v>139273280</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6">
         <v>0</v>
       </c>
-      <c r="I75" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="6">
         <v>70</v>
       </c>
@@ -2645,17 +2350,13 @@
         <v>17000000</v>
       </c>
       <c r="G76" s="6">
-        <f t="shared" si="1"/>
-        <v>156273280</v>
+        <v>0</v>
       </c>
       <c r="H76" s="6">
         <v>0</v>
       </c>
-      <c r="I76" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="6">
         <v>71</v>
       </c>
@@ -2672,17 +2373,13 @@
         <v>20000000</v>
       </c>
       <c r="G77" s="6">
-        <f t="shared" ref="G77:G105" si="2">SUM(G76,F77)</f>
-        <v>176273280</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6">
         <v>0</v>
       </c>
-      <c r="I77" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="6">
         <v>72</v>
       </c>
@@ -2699,17 +2396,13 @@
         <v>23000000</v>
       </c>
       <c r="G78" s="6">
-        <f t="shared" si="2"/>
-        <v>199273280</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6">
         <v>0</v>
       </c>
-      <c r="I78" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="6">
         <v>73</v>
       </c>
@@ -2726,17 +2419,13 @@
         <v>25000000</v>
       </c>
       <c r="G79" s="6">
-        <f t="shared" si="2"/>
-        <v>224273280</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6">
         <v>0</v>
       </c>
-      <c r="I79" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="6">
         <v>74</v>
       </c>
@@ -2753,17 +2442,13 @@
         <v>30000000</v>
       </c>
       <c r="G80" s="6">
-        <f t="shared" si="2"/>
-        <v>254273280</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6">
         <v>0</v>
       </c>
-      <c r="I80" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="6">
         <v>75</v>
       </c>
@@ -2780,17 +2465,13 @@
         <v>35000000</v>
       </c>
       <c r="G81" s="6">
-        <f t="shared" si="2"/>
-        <v>289273280</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6">
         <v>0</v>
       </c>
-      <c r="I81" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="6">
         <v>76</v>
       </c>
@@ -2807,17 +2488,13 @@
         <v>40000000</v>
       </c>
       <c r="G82" s="6">
-        <f t="shared" si="2"/>
-        <v>329273280</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6">
         <v>0</v>
       </c>
-      <c r="I82" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="6">
         <v>77</v>
       </c>
@@ -2834,17 +2511,13 @@
         <v>45000000</v>
       </c>
       <c r="G83" s="6">
-        <f t="shared" si="2"/>
-        <v>374273280</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6">
         <v>0</v>
       </c>
-      <c r="I83" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="6">
         <v>78</v>
       </c>
@@ -2861,17 +2534,13 @@
         <v>50000000</v>
       </c>
       <c r="G84" s="6">
-        <f t="shared" si="2"/>
-        <v>424273280</v>
+        <v>0</v>
       </c>
       <c r="H84" s="6">
         <v>0</v>
       </c>
-      <c r="I84" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="6">
         <v>79</v>
       </c>
@@ -2888,17 +2557,13 @@
         <v>50000000</v>
       </c>
       <c r="G85" s="6">
-        <f t="shared" si="2"/>
-        <v>474273280</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6">
         <v>0</v>
       </c>
-      <c r="I85" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="6">
         <v>80</v>
       </c>
@@ -2915,17 +2580,13 @@
         <v>55000000</v>
       </c>
       <c r="G86" s="6">
-        <f t="shared" si="2"/>
-        <v>529273280</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6">
         <v>0</v>
       </c>
-      <c r="I86" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="6">
         <v>81</v>
       </c>
@@ -2942,17 +2603,13 @@
         <v>60000000</v>
       </c>
       <c r="G87" s="6">
-        <f t="shared" si="2"/>
-        <v>589273280</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6">
         <v>0</v>
       </c>
-      <c r="I87" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="6">
         <v>82</v>
       </c>
@@ -2969,17 +2626,13 @@
         <v>65000000</v>
       </c>
       <c r="G88" s="6">
-        <f t="shared" si="2"/>
-        <v>654273280</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6">
         <v>0</v>
       </c>
-      <c r="I88" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="6">
         <v>83</v>
       </c>
@@ -2996,17 +2649,13 @@
         <v>70000000</v>
       </c>
       <c r="G89" s="6">
-        <f t="shared" si="2"/>
-        <v>724273280</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6">
         <v>0</v>
       </c>
-      <c r="I89" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="6">
         <v>84</v>
       </c>
@@ -3023,17 +2672,13 @@
         <v>80000000</v>
       </c>
       <c r="G90" s="6">
-        <f t="shared" si="2"/>
-        <v>804273280</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6">
         <v>0</v>
       </c>
-      <c r="I90" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="6">
         <v>85</v>
       </c>
@@ -3050,17 +2695,13 @@
         <v>95000000</v>
       </c>
       <c r="G91" s="6">
-        <f t="shared" si="2"/>
-        <v>899273280</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6">
         <v>0</v>
       </c>
-      <c r="I91" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="6">
         <v>86</v>
       </c>
@@ -3077,17 +2718,13 @@
         <v>95000000</v>
       </c>
       <c r="G92" s="6">
-        <f t="shared" si="2"/>
-        <v>994273280</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6">
         <v>0</v>
       </c>
-      <c r="I92" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="6">
         <v>87</v>
       </c>
@@ -3104,17 +2741,13 @@
         <v>105000000</v>
       </c>
       <c r="G93" s="6">
-        <f t="shared" si="2"/>
-        <v>1099273280</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6">
         <v>0</v>
       </c>
-      <c r="I93" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="6">
         <v>88</v>
       </c>
@@ -3131,17 +2764,13 @@
         <v>105000000</v>
       </c>
       <c r="G94" s="6">
-        <f t="shared" si="2"/>
-        <v>1204273280</v>
+        <v>0</v>
       </c>
       <c r="H94" s="6">
         <v>0</v>
       </c>
-      <c r="I94" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="6">
         <v>89</v>
       </c>
@@ -3158,17 +2787,13 @@
         <v>145000000</v>
       </c>
       <c r="G95" s="6">
-        <f t="shared" si="2"/>
-        <v>1349273280</v>
+        <v>0</v>
       </c>
       <c r="H95" s="6">
         <v>0</v>
       </c>
-      <c r="I95" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="6">
         <v>90</v>
       </c>
@@ -3185,17 +2810,13 @@
         <v>130000000</v>
       </c>
       <c r="G96" s="6">
-        <f t="shared" si="2"/>
-        <v>1479273280</v>
+        <v>0</v>
       </c>
       <c r="H96" s="6">
         <v>0</v>
       </c>
-      <c r="I96" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B97" s="6">
         <v>91</v>
       </c>
@@ -3212,17 +2833,13 @@
         <v>100000000</v>
       </c>
       <c r="G97" s="6">
-        <f t="shared" si="2"/>
-        <v>1579273280</v>
+        <v>0</v>
       </c>
       <c r="H97" s="6">
         <v>0</v>
       </c>
-      <c r="I97" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B98" s="6">
         <v>92</v>
       </c>
@@ -3239,17 +2856,13 @@
         <v>100000000</v>
       </c>
       <c r="G98" s="6">
-        <f t="shared" si="2"/>
-        <v>1679273280</v>
+        <v>0</v>
       </c>
       <c r="H98" s="6">
         <v>0</v>
       </c>
-      <c r="I98" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B99" s="6">
         <v>93</v>
       </c>
@@ -3266,17 +2879,13 @@
         <v>110000000</v>
       </c>
       <c r="G99" s="6">
-        <f t="shared" si="2"/>
-        <v>1789273280</v>
+        <v>0</v>
       </c>
       <c r="H99" s="6">
         <v>0</v>
       </c>
-      <c r="I99" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B100" s="6">
         <v>94</v>
       </c>
@@ -3293,17 +2902,13 @@
         <v>120000000</v>
       </c>
       <c r="G100" s="6">
-        <f t="shared" si="2"/>
-        <v>1909273280</v>
+        <v>0</v>
       </c>
       <c r="H100" s="6">
         <v>0</v>
       </c>
-      <c r="I100" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B101" s="6">
         <v>95</v>
       </c>
@@ -3320,17 +2925,13 @@
         <v>130000000</v>
       </c>
       <c r="G101" s="6">
-        <f t="shared" si="2"/>
-        <v>2039273280</v>
+        <v>0</v>
       </c>
       <c r="H101" s="6">
         <v>0</v>
       </c>
-      <c r="I101" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B102" s="6">
         <v>96</v>
       </c>
@@ -3347,17 +2948,13 @@
         <v>120000000</v>
       </c>
       <c r="G102" s="6">
-        <f t="shared" si="2"/>
-        <v>2159273280</v>
+        <v>0</v>
       </c>
       <c r="H102" s="6">
         <v>0</v>
       </c>
-      <c r="I102" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B103" s="6">
         <v>97</v>
       </c>
@@ -3374,17 +2971,13 @@
         <v>220000000</v>
       </c>
       <c r="G103" s="6">
-        <f t="shared" si="2"/>
-        <v>2379273280</v>
+        <v>0</v>
       </c>
       <c r="H103" s="6">
         <v>0</v>
       </c>
-      <c r="I103" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B104" s="6">
         <v>98</v>
       </c>
@@ -3401,17 +2994,13 @@
         <v>230000000</v>
       </c>
       <c r="G104" s="6">
-        <f t="shared" si="2"/>
-        <v>2609273280</v>
+        <v>0</v>
       </c>
       <c r="H104" s="6">
         <v>0</v>
       </c>
-      <c r="I104" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B105" s="6">
         <v>99</v>
       </c>
@@ -3428,28 +3017,24 @@
         <v>0</v>
       </c>
       <c r="G105" s="6">
-        <f t="shared" si="2"/>
-        <v>2609273280</v>
+        <v>0</v>
       </c>
       <c r="H105" s="6">
         <v>0</v>
       </c>
-      <c r="I105" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
+      <c r="G106" s="6"/>
       <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="1">
         <v>5</v>
@@ -3466,18 +3051,14 @@
       <c r="F107" s="6">
         <v>960</v>
       </c>
-      <c r="G107" s="6">
-        <f>SUM(G9,F107)</f>
-        <v>2160</v>
+      <c r="G107" s="1">
+        <v>0</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
       </c>
-      <c r="I107" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="1">
         <v>6</v>
@@ -3494,18 +3075,14 @@
       <c r="F108" s="6">
         <v>1080</v>
       </c>
-      <c r="G108" s="6">
-        <f>SUM(G107,F108)</f>
-        <v>3240</v>
+      <c r="G108" s="1">
+        <v>0</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
       </c>
-      <c r="I108" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="1">
         <v>7</v>
@@ -3522,18 +3099,14 @@
       <c r="F109" s="6">
         <v>1080</v>
       </c>
-      <c r="G109" s="6">
-        <f t="shared" ref="G109:G172" si="3">SUM(G108,F109)</f>
-        <v>4320</v>
+      <c r="G109" s="1">
+        <v>0</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
       </c>
-      <c r="I109" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="1">
         <v>8</v>
@@ -3550,18 +3123,14 @@
       <c r="F110" s="6">
         <v>1080</v>
       </c>
-      <c r="G110" s="6">
-        <f t="shared" si="3"/>
-        <v>5400</v>
+      <c r="G110" s="1">
+        <v>0</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
       </c>
-      <c r="I110" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="6"/>
       <c r="B111" s="1">
         <v>9</v>
@@ -3578,18 +3147,14 @@
       <c r="F111" s="6">
         <v>2160</v>
       </c>
-      <c r="G111" s="6">
-        <f t="shared" si="3"/>
-        <v>7560</v>
+      <c r="G111" s="1">
+        <v>0</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
       </c>
-      <c r="I111" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="6"/>
       <c r="B112" s="1">
         <v>10</v>
@@ -3606,18 +3171,14 @@
       <c r="F112" s="6">
         <v>2160</v>
       </c>
-      <c r="G112" s="6">
-        <f t="shared" si="3"/>
-        <v>9720</v>
+      <c r="G112" s="1">
+        <v>0</v>
       </c>
       <c r="H112" s="1">
         <v>0</v>
       </c>
-      <c r="I112" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="6"/>
       <c r="B113" s="1">
         <v>11</v>
@@ -3634,18 +3195,14 @@
       <c r="F113" s="6">
         <v>2160</v>
       </c>
-      <c r="G113" s="6">
-        <f t="shared" si="3"/>
-        <v>11880</v>
+      <c r="G113" s="1">
+        <v>0</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
       </c>
-      <c r="I113" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="6"/>
       <c r="B114" s="1">
         <v>12</v>
@@ -3662,18 +3219,14 @@
       <c r="F114" s="6">
         <v>4320</v>
       </c>
-      <c r="G114" s="6">
-        <f t="shared" si="3"/>
-        <v>16200</v>
+      <c r="G114" s="1">
+        <v>0</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
       </c>
-      <c r="I114" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="6"/>
       <c r="B115" s="1">
         <v>13</v>
@@ -3690,18 +3243,14 @@
       <c r="F115" s="6">
         <v>4320</v>
       </c>
-      <c r="G115" s="6">
-        <f t="shared" si="3"/>
-        <v>20520</v>
+      <c r="G115" s="1">
+        <v>0</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
       </c>
-      <c r="I115" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="6"/>
       <c r="B116" s="1">
         <v>14</v>
@@ -3718,18 +3267,14 @@
       <c r="F116" s="6">
         <v>4320</v>
       </c>
-      <c r="G116" s="6">
-        <f t="shared" si="3"/>
-        <v>24840</v>
+      <c r="G116" s="1">
+        <v>0</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
       </c>
-      <c r="I116" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="6"/>
       <c r="B117" s="1">
         <v>15</v>
@@ -3746,18 +3291,14 @@
       <c r="F117" s="6">
         <v>8640</v>
       </c>
-      <c r="G117" s="6">
-        <f t="shared" si="3"/>
-        <v>33480</v>
+      <c r="G117" s="1">
+        <v>0</v>
       </c>
       <c r="H117" s="1">
         <v>0</v>
       </c>
-      <c r="I117" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="6"/>
       <c r="B118" s="1">
         <v>16</v>
@@ -3774,18 +3315,14 @@
       <c r="F118" s="6">
         <v>8640</v>
       </c>
-      <c r="G118" s="6">
-        <f t="shared" si="3"/>
-        <v>42120</v>
+      <c r="G118" s="1">
+        <v>0</v>
       </c>
       <c r="H118" s="1">
         <v>0</v>
       </c>
-      <c r="I118" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="6"/>
       <c r="B119" s="1">
         <v>17</v>
@@ -3802,18 +3339,14 @@
       <c r="F119" s="6">
         <v>8640</v>
       </c>
-      <c r="G119" s="6">
-        <f t="shared" si="3"/>
-        <v>50760</v>
+      <c r="G119" s="1">
+        <v>0</v>
       </c>
       <c r="H119" s="1">
         <v>0</v>
       </c>
-      <c r="I119" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="6"/>
       <c r="B120" s="1">
         <v>18</v>
@@ -3830,18 +3363,14 @@
       <c r="F120" s="6">
         <v>17280</v>
       </c>
-      <c r="G120" s="6">
-        <f t="shared" si="3"/>
-        <v>68040</v>
+      <c r="G120" s="1">
+        <v>0</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
       </c>
-      <c r="I120" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="6"/>
       <c r="B121" s="1">
         <v>19</v>
@@ -3858,18 +3387,14 @@
       <c r="F121" s="6">
         <v>17280</v>
       </c>
-      <c r="G121" s="6">
-        <f t="shared" si="3"/>
-        <v>85320</v>
+      <c r="G121" s="1">
+        <v>0</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
       </c>
-      <c r="I121" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="6"/>
       <c r="B122" s="1">
         <v>20</v>
@@ -3886,18 +3411,14 @@
       <c r="F122" s="6">
         <v>17280</v>
       </c>
-      <c r="G122" s="6">
-        <f t="shared" si="3"/>
-        <v>102600</v>
+      <c r="G122" s="1">
+        <v>0</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
       </c>
-      <c r="I122" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="6"/>
       <c r="B123" s="1">
         <v>21</v>
@@ -3914,18 +3435,14 @@
       <c r="F123" s="6">
         <v>34560</v>
       </c>
-      <c r="G123" s="6">
-        <f t="shared" si="3"/>
-        <v>137160</v>
+      <c r="G123" s="1">
+        <v>0</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
       </c>
-      <c r="I123" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="6"/>
       <c r="B124" s="1">
         <v>22</v>
@@ -3942,18 +3459,14 @@
       <c r="F124" s="6">
         <v>34560</v>
       </c>
-      <c r="G124" s="6">
-        <f t="shared" si="3"/>
-        <v>171720</v>
+      <c r="G124" s="1">
+        <v>0</v>
       </c>
       <c r="H124" s="1">
         <v>0</v>
       </c>
-      <c r="I124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="6"/>
       <c r="B125" s="1">
         <v>23</v>
@@ -3970,18 +3483,14 @@
       <c r="F125" s="6">
         <v>34560</v>
       </c>
-      <c r="G125" s="6">
-        <f t="shared" si="3"/>
-        <v>206280</v>
+      <c r="G125" s="1">
+        <v>0</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
       </c>
-      <c r="I125" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="6"/>
       <c r="B126" s="1">
         <v>24</v>
@@ -3998,18 +3507,14 @@
       <c r="F126" s="6">
         <v>69120</v>
       </c>
-      <c r="G126" s="6">
-        <f t="shared" si="3"/>
-        <v>275400</v>
+      <c r="G126" s="1">
+        <v>0</v>
       </c>
       <c r="H126" s="1">
         <v>0</v>
       </c>
-      <c r="I126" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="6"/>
       <c r="B127" s="1">
         <v>25</v>
@@ -4026,18 +3531,14 @@
       <c r="F127" s="6">
         <v>69120</v>
       </c>
-      <c r="G127" s="6">
-        <f t="shared" si="3"/>
-        <v>344520</v>
+      <c r="G127" s="1">
+        <v>0</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
       </c>
-      <c r="I127" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="6"/>
       <c r="B128" s="1">
         <v>26</v>
@@ -4054,18 +3555,14 @@
       <c r="F128" s="6">
         <v>69120</v>
       </c>
-      <c r="G128" s="6">
-        <f t="shared" si="3"/>
-        <v>413640</v>
+      <c r="G128" s="1">
+        <v>0</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
       </c>
-      <c r="I128" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="6"/>
       <c r="B129" s="1">
         <v>27</v>
@@ -4082,18 +3579,14 @@
       <c r="F129" s="6">
         <v>138240</v>
       </c>
-      <c r="G129" s="6">
-        <f t="shared" si="3"/>
-        <v>551880</v>
+      <c r="G129" s="1">
+        <v>0</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
       </c>
-      <c r="I129" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="6"/>
       <c r="B130" s="1">
         <v>28</v>
@@ -4110,18 +3603,14 @@
       <c r="F130" s="6">
         <v>138240</v>
       </c>
-      <c r="G130" s="6">
-        <f t="shared" si="3"/>
-        <v>690120</v>
+      <c r="G130" s="1">
+        <v>0</v>
       </c>
       <c r="H130" s="1">
         <v>0</v>
       </c>
-      <c r="I130" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="6"/>
       <c r="B131" s="1">
         <v>29</v>
@@ -4138,18 +3627,14 @@
       <c r="F131" s="6">
         <v>138240</v>
       </c>
-      <c r="G131" s="6">
-        <f t="shared" si="3"/>
-        <v>828360</v>
+      <c r="G131" s="1">
+        <v>0</v>
       </c>
       <c r="H131" s="1">
         <v>0</v>
       </c>
-      <c r="I131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="6"/>
       <c r="B132" s="1">
         <v>30</v>
@@ -4166,18 +3651,14 @@
       <c r="F132" s="6">
         <v>200000</v>
       </c>
-      <c r="G132" s="6">
-        <f t="shared" si="3"/>
-        <v>1028360</v>
+      <c r="G132" s="1">
+        <v>0</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
       </c>
-      <c r="I132" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="6"/>
       <c r="B133" s="1">
         <v>31</v>
@@ -4194,18 +3675,14 @@
       <c r="F133" s="6">
         <v>200000</v>
       </c>
-      <c r="G133" s="6">
-        <f t="shared" si="3"/>
-        <v>1228360</v>
+      <c r="G133" s="1">
+        <v>0</v>
       </c>
       <c r="H133" s="1">
         <v>0</v>
       </c>
-      <c r="I133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="6"/>
       <c r="B134" s="1">
         <v>32</v>
@@ -4222,18 +3699,14 @@
       <c r="F134" s="6">
         <v>200000</v>
       </c>
-      <c r="G134" s="6">
-        <f t="shared" si="3"/>
-        <v>1428360</v>
+      <c r="G134" s="1">
+        <v>0</v>
       </c>
       <c r="H134" s="1">
         <v>0</v>
       </c>
-      <c r="I134" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="6"/>
       <c r="B135" s="1">
         <v>33</v>
@@ -4250,18 +3723,14 @@
       <c r="F135" s="6">
         <v>270000</v>
       </c>
-      <c r="G135" s="6">
-        <f t="shared" si="3"/>
-        <v>1698360</v>
+      <c r="G135" s="1">
+        <v>0</v>
       </c>
       <c r="H135" s="1">
         <v>0</v>
       </c>
-      <c r="I135" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="6"/>
       <c r="B136" s="1">
         <v>34</v>
@@ -4278,18 +3747,14 @@
       <c r="F136" s="6">
         <v>270000</v>
       </c>
-      <c r="G136" s="6">
-        <f t="shared" si="3"/>
-        <v>1968360</v>
+      <c r="G136" s="1">
+        <v>0</v>
       </c>
       <c r="H136" s="1">
         <v>0</v>
       </c>
-      <c r="I136" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="1">
         <v>35</v>
@@ -4306,18 +3771,14 @@
       <c r="F137" s="6">
         <v>270000</v>
       </c>
-      <c r="G137" s="6">
-        <f t="shared" si="3"/>
-        <v>2238360</v>
+      <c r="G137" s="1">
+        <v>0</v>
       </c>
       <c r="H137" s="1">
         <v>0</v>
       </c>
-      <c r="I137" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="6"/>
       <c r="B138" s="1">
         <v>36</v>
@@ -4334,18 +3795,14 @@
       <c r="F138" s="6">
         <v>410000</v>
       </c>
-      <c r="G138" s="6">
-        <f t="shared" si="3"/>
-        <v>2648360</v>
+      <c r="G138" s="1">
+        <v>0</v>
       </c>
       <c r="H138" s="1">
         <v>0</v>
       </c>
-      <c r="I138" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="6"/>
       <c r="B139" s="1">
         <v>37</v>
@@ -4362,18 +3819,14 @@
       <c r="F139" s="6">
         <v>410000</v>
       </c>
-      <c r="G139" s="6">
-        <f t="shared" si="3"/>
-        <v>3058360</v>
+      <c r="G139" s="1">
+        <v>0</v>
       </c>
       <c r="H139" s="1">
         <v>0</v>
       </c>
-      <c r="I139" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="6"/>
       <c r="B140" s="1">
         <v>38</v>
@@ -4390,18 +3843,14 @@
       <c r="F140" s="6">
         <v>410000</v>
       </c>
-      <c r="G140" s="6">
-        <f t="shared" si="3"/>
-        <v>3468360</v>
+      <c r="G140" s="1">
+        <v>0</v>
       </c>
       <c r="H140" s="1">
         <v>0</v>
       </c>
-      <c r="I140" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="6"/>
       <c r="B141" s="1">
         <v>39</v>
@@ -4418,18 +3867,14 @@
       <c r="F141" s="6">
         <v>440000</v>
       </c>
-      <c r="G141" s="6">
-        <f t="shared" si="3"/>
-        <v>3908360</v>
+      <c r="G141" s="1">
+        <v>0</v>
       </c>
       <c r="H141" s="1">
         <v>0</v>
       </c>
-      <c r="I141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="6"/>
       <c r="B142" s="1">
         <v>40</v>
@@ -4446,18 +3891,14 @@
       <c r="F142" s="6">
         <v>440000</v>
       </c>
-      <c r="G142" s="6">
-        <f t="shared" si="3"/>
-        <v>4348360</v>
+      <c r="G142" s="1">
+        <v>0</v>
       </c>
       <c r="H142" s="1">
         <v>0</v>
       </c>
-      <c r="I142" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="6"/>
       <c r="B143" s="1">
         <v>41</v>
@@ -4474,18 +3915,14 @@
       <c r="F143" s="6">
         <v>440000</v>
       </c>
-      <c r="G143" s="6">
-        <f t="shared" si="3"/>
-        <v>4788360</v>
+      <c r="G143" s="1">
+        <v>0</v>
       </c>
       <c r="H143" s="1">
         <v>0</v>
       </c>
-      <c r="I143" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="6"/>
       <c r="B144" s="1">
         <v>42</v>
@@ -4502,18 +3939,14 @@
       <c r="F144" s="6">
         <v>650000</v>
       </c>
-      <c r="G144" s="6">
-        <f t="shared" si="3"/>
-        <v>5438360</v>
+      <c r="G144" s="1">
+        <v>0</v>
       </c>
       <c r="H144" s="1">
         <v>0</v>
       </c>
-      <c r="I144" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="6"/>
       <c r="B145" s="1">
         <v>43</v>
@@ -4530,18 +3963,14 @@
       <c r="F145" s="6">
         <v>650000</v>
       </c>
-      <c r="G145" s="6">
-        <f t="shared" si="3"/>
-        <v>6088360</v>
+      <c r="G145" s="1">
+        <v>0</v>
       </c>
       <c r="H145" s="1">
         <v>0</v>
       </c>
-      <c r="I145" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="6"/>
       <c r="B146" s="1">
         <v>44</v>
@@ -4558,18 +3987,14 @@
       <c r="F146" s="6">
         <v>650000</v>
       </c>
-      <c r="G146" s="6">
-        <f t="shared" si="3"/>
-        <v>6738360</v>
+      <c r="G146" s="1">
+        <v>0</v>
       </c>
       <c r="H146" s="1">
         <v>0</v>
       </c>
-      <c r="I146" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="6"/>
       <c r="B147" s="1">
         <v>45</v>
@@ -4586,18 +4011,14 @@
       <c r="F147" s="6">
         <v>880000</v>
       </c>
-      <c r="G147" s="6">
-        <f t="shared" si="3"/>
-        <v>7618360</v>
+      <c r="G147" s="1">
+        <v>0</v>
       </c>
       <c r="H147" s="1">
         <v>0</v>
       </c>
-      <c r="I147" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="6"/>
       <c r="B148" s="1">
         <v>46</v>
@@ -4614,18 +4035,14 @@
       <c r="F148" s="6">
         <v>880000</v>
       </c>
-      <c r="G148" s="6">
-        <f t="shared" si="3"/>
-        <v>8498360</v>
+      <c r="G148" s="1">
+        <v>0</v>
       </c>
       <c r="H148" s="1">
         <v>0</v>
       </c>
-      <c r="I148" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="6"/>
       <c r="B149" s="1">
         <v>47</v>
@@ -4642,18 +4059,14 @@
       <c r="F149" s="6">
         <v>880000</v>
       </c>
-      <c r="G149" s="6">
-        <f t="shared" si="3"/>
-        <v>9378360</v>
+      <c r="G149" s="1">
+        <v>0</v>
       </c>
       <c r="H149" s="1">
         <v>0</v>
       </c>
-      <c r="I149" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="6"/>
       <c r="B150" s="1">
         <v>48</v>
@@ -4670,18 +4083,14 @@
       <c r="F150" s="6">
         <v>1300000</v>
       </c>
-      <c r="G150" s="6">
-        <f t="shared" si="3"/>
-        <v>10678360</v>
+      <c r="G150" s="1">
+        <v>0</v>
       </c>
       <c r="H150" s="1">
         <v>0</v>
       </c>
-      <c r="I150" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="6"/>
       <c r="B151" s="1">
         <v>49</v>
@@ -4698,18 +4107,14 @@
       <c r="F151" s="6">
         <v>1300000</v>
       </c>
-      <c r="G151" s="6">
-        <f t="shared" si="3"/>
-        <v>11978360</v>
+      <c r="G151" s="1">
+        <v>0</v>
       </c>
       <c r="H151" s="1">
         <v>0</v>
       </c>
-      <c r="I151" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="6"/>
       <c r="B152" s="1">
         <v>50</v>
@@ -4726,18 +4131,14 @@
       <c r="F152" s="6">
         <v>1300000</v>
       </c>
-      <c r="G152" s="6">
-        <f t="shared" si="3"/>
-        <v>13278360</v>
+      <c r="G152" s="1">
+        <v>0</v>
       </c>
       <c r="H152" s="1">
         <v>0</v>
       </c>
-      <c r="I152" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="6"/>
       <c r="B153" s="1">
         <v>51</v>
@@ -4754,18 +4155,14 @@
       <c r="F153" s="6">
         <v>1470000</v>
       </c>
-      <c r="G153" s="6">
-        <f t="shared" si="3"/>
-        <v>14748360</v>
+      <c r="G153" s="1">
+        <v>0</v>
       </c>
       <c r="H153" s="1">
         <v>0</v>
       </c>
-      <c r="I153" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="6"/>
       <c r="B154" s="1">
         <v>52</v>
@@ -4782,18 +4179,14 @@
       <c r="F154" s="6">
         <v>1470000</v>
       </c>
-      <c r="G154" s="6">
-        <f t="shared" si="3"/>
-        <v>16218360</v>
+      <c r="G154" s="1">
+        <v>0</v>
       </c>
       <c r="H154" s="1">
         <v>0</v>
       </c>
-      <c r="I154" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="6"/>
       <c r="B155" s="1">
         <v>53</v>
@@ -4810,18 +4203,14 @@
       <c r="F155" s="6">
         <v>1470000</v>
       </c>
-      <c r="G155" s="6">
-        <f t="shared" si="3"/>
-        <v>17688360</v>
+      <c r="G155" s="1">
+        <v>0</v>
       </c>
       <c r="H155" s="1">
         <v>0</v>
       </c>
-      <c r="I155" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="6"/>
       <c r="B156" s="1">
         <v>54</v>
@@ -4838,18 +4227,14 @@
       <c r="F156" s="6">
         <v>2160000</v>
       </c>
-      <c r="G156" s="6">
-        <f t="shared" si="3"/>
-        <v>19848360</v>
+      <c r="G156" s="1">
+        <v>0</v>
       </c>
       <c r="H156" s="1">
         <v>0</v>
       </c>
-      <c r="I156" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="6"/>
       <c r="B157" s="1">
         <v>55</v>
@@ -4866,18 +4251,14 @@
       <c r="F157" s="6">
         <v>2160000</v>
       </c>
-      <c r="G157" s="6">
-        <f t="shared" si="3"/>
-        <v>22008360</v>
+      <c r="G157" s="1">
+        <v>0</v>
       </c>
       <c r="H157" s="1">
         <v>0</v>
       </c>
-      <c r="I157" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="6"/>
       <c r="B158" s="1">
         <v>56</v>
@@ -4894,18 +4275,14 @@
       <c r="F158" s="6">
         <v>2160000</v>
       </c>
-      <c r="G158" s="6">
-        <f t="shared" si="3"/>
-        <v>24168360</v>
+      <c r="G158" s="1">
+        <v>0</v>
       </c>
       <c r="H158" s="1">
         <v>0</v>
       </c>
-      <c r="I158" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="6"/>
       <c r="B159" s="1">
         <v>57</v>
@@ -4922,18 +4299,14 @@
       <c r="F159" s="6">
         <v>2850000</v>
       </c>
-      <c r="G159" s="6">
-        <f t="shared" si="3"/>
-        <v>27018360</v>
+      <c r="G159" s="1">
+        <v>0</v>
       </c>
       <c r="H159" s="1">
         <v>0</v>
       </c>
-      <c r="I159" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="6"/>
       <c r="B160" s="1">
         <v>58</v>
@@ -4950,18 +4323,14 @@
       <c r="F160" s="6">
         <v>4850000</v>
       </c>
-      <c r="G160" s="6">
-        <f t="shared" si="3"/>
-        <v>31868360</v>
+      <c r="G160" s="1">
+        <v>0</v>
       </c>
       <c r="H160" s="1">
         <v>0</v>
       </c>
-      <c r="I160" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="6"/>
       <c r="B161" s="1">
         <v>59</v>
@@ -4978,18 +4347,14 @@
       <c r="F161" s="6">
         <v>4850000</v>
       </c>
-      <c r="G161" s="6">
-        <f t="shared" si="3"/>
-        <v>36718360</v>
+      <c r="G161" s="1">
+        <v>0</v>
       </c>
       <c r="H161" s="1">
         <v>0</v>
       </c>
-      <c r="I161" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="6"/>
       <c r="B162" s="1">
         <v>60</v>
@@ -5006,18 +4371,14 @@
       <c r="F162" s="6">
         <v>5760000</v>
       </c>
-      <c r="G162" s="6">
-        <f t="shared" si="3"/>
-        <v>42478360</v>
+      <c r="G162" s="1">
+        <v>0</v>
       </c>
       <c r="H162" s="1">
         <v>0</v>
       </c>
-      <c r="I162" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="6"/>
       <c r="B163" s="1">
         <v>61</v>
@@ -5034,18 +4395,14 @@
       <c r="F163" s="6">
         <v>6760000</v>
       </c>
-      <c r="G163" s="6">
-        <f t="shared" si="3"/>
-        <v>49238360</v>
+      <c r="G163" s="1">
+        <v>0</v>
       </c>
       <c r="H163" s="1">
         <v>0</v>
       </c>
-      <c r="I163" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="6"/>
       <c r="B164" s="1">
         <v>62</v>
@@ -5062,18 +4419,14 @@
       <c r="F164" s="6">
         <v>7760000</v>
       </c>
-      <c r="G164" s="6">
-        <f t="shared" si="3"/>
-        <v>56998360</v>
+      <c r="G164" s="1">
+        <v>0</v>
       </c>
       <c r="H164" s="1">
         <v>0</v>
       </c>
-      <c r="I164" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="6"/>
       <c r="B165" s="1">
         <v>63</v>
@@ -5090,18 +4443,14 @@
       <c r="F165" s="6">
         <v>8490000</v>
       </c>
-      <c r="G165" s="6">
-        <f t="shared" si="3"/>
-        <v>65488360</v>
+      <c r="G165" s="1">
+        <v>0</v>
       </c>
       <c r="H165" s="1">
         <v>0</v>
       </c>
-      <c r="I165" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="6"/>
       <c r="B166" s="1">
         <v>64</v>
@@ -5118,18 +4467,14 @@
       <c r="F166" s="6">
         <v>7490000</v>
       </c>
-      <c r="G166" s="6">
-        <f t="shared" si="3"/>
-        <v>72978360</v>
+      <c r="G166" s="1">
+        <v>0</v>
       </c>
       <c r="H166" s="1">
         <v>0</v>
       </c>
-      <c r="I166" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="6"/>
       <c r="B167" s="1">
         <v>65</v>
@@ -5146,18 +4491,14 @@
       <c r="F167" s="6">
         <v>8490000</v>
       </c>
-      <c r="G167" s="6">
-        <f t="shared" si="3"/>
-        <v>81468360</v>
+      <c r="G167" s="1">
+        <v>0</v>
       </c>
       <c r="H167" s="1">
         <v>0</v>
       </c>
-      <c r="I167" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="6"/>
       <c r="B168" s="1">
         <v>66</v>
@@ -5174,18 +4515,14 @@
       <c r="F168" s="6">
         <v>9710000</v>
       </c>
-      <c r="G168" s="6">
-        <f t="shared" si="3"/>
-        <v>91178360</v>
+      <c r="G168" s="1">
+        <v>0</v>
       </c>
       <c r="H168" s="1">
         <v>0</v>
       </c>
-      <c r="I168" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="6"/>
       <c r="B169" s="1">
         <v>67</v>
@@ -5202,18 +4539,14 @@
       <c r="F169" s="6">
         <v>8800000</v>
       </c>
-      <c r="G169" s="6">
-        <f t="shared" si="3"/>
-        <v>99978360</v>
+      <c r="G169" s="1">
+        <v>0</v>
       </c>
       <c r="H169" s="1">
         <v>0</v>
       </c>
-      <c r="I169" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="6"/>
       <c r="B170" s="1">
         <v>68</v>
@@ -5230,18 +4563,14 @@
       <c r="F170" s="6">
         <v>10000000</v>
       </c>
-      <c r="G170" s="6">
-        <f t="shared" si="3"/>
-        <v>109978360</v>
+      <c r="G170" s="1">
+        <v>0</v>
       </c>
       <c r="H170" s="1">
         <v>0</v>
       </c>
-      <c r="I170" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="6"/>
       <c r="B171" s="1">
         <v>69</v>
@@ -5258,18 +4587,14 @@
       <c r="F171" s="6">
         <v>23000000</v>
       </c>
-      <c r="G171" s="6">
-        <f t="shared" si="3"/>
-        <v>132978360</v>
+      <c r="G171" s="1">
+        <v>0</v>
       </c>
       <c r="H171" s="1">
         <v>0</v>
       </c>
-      <c r="I171" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="6"/>
       <c r="B172" s="1">
         <v>70</v>
@@ -5286,18 +4611,14 @@
       <c r="F172" s="6">
         <v>21000000</v>
       </c>
-      <c r="G172" s="6">
-        <f t="shared" si="3"/>
-        <v>153978360</v>
+      <c r="G172" s="1">
+        <v>0</v>
       </c>
       <c r="H172" s="1">
         <v>0</v>
       </c>
-      <c r="I172" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="6"/>
       <c r="B173" s="1">
         <v>71</v>
@@ -5314,18 +4635,14 @@
       <c r="F173" s="6">
         <v>26000000</v>
       </c>
-      <c r="G173" s="6">
-        <f t="shared" ref="G173:G201" si="4">SUM(G172,F173)</f>
-        <v>179978360</v>
+      <c r="G173" s="1">
+        <v>0</v>
       </c>
       <c r="H173" s="1">
         <v>0</v>
       </c>
-      <c r="I173" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="6"/>
       <c r="B174" s="1">
         <v>72</v>
@@ -5342,18 +4659,14 @@
       <c r="F174" s="6">
         <v>30000000</v>
       </c>
-      <c r="G174" s="6">
-        <f t="shared" si="4"/>
-        <v>209978360</v>
+      <c r="G174" s="1">
+        <v>0</v>
       </c>
       <c r="H174" s="1">
         <v>0</v>
       </c>
-      <c r="I174" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="6"/>
       <c r="B175" s="1">
         <v>73</v>
@@ -5370,18 +4683,14 @@
       <c r="F175" s="6">
         <v>35000000</v>
       </c>
-      <c r="G175" s="6">
-        <f t="shared" si="4"/>
-        <v>244978360</v>
+      <c r="G175" s="1">
+        <v>0</v>
       </c>
       <c r="H175" s="1">
         <v>0</v>
       </c>
-      <c r="I175" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="6"/>
       <c r="B176" s="1">
         <v>74</v>
@@ -5398,18 +4707,14 @@
       <c r="F176" s="6">
         <v>35000000</v>
       </c>
-      <c r="G176" s="6">
-        <f t="shared" si="4"/>
-        <v>279978360</v>
+      <c r="G176" s="1">
+        <v>0</v>
       </c>
       <c r="H176" s="1">
         <v>0</v>
       </c>
-      <c r="I176" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="6"/>
       <c r="B177" s="1">
         <v>75</v>
@@ -5426,18 +4731,14 @@
       <c r="F177" s="6">
         <v>50000000</v>
       </c>
-      <c r="G177" s="6">
-        <f t="shared" si="4"/>
-        <v>329978360</v>
+      <c r="G177" s="1">
+        <v>0</v>
       </c>
       <c r="H177" s="1">
         <v>0</v>
       </c>
-      <c r="I177" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="6"/>
       <c r="B178" s="1">
         <v>76</v>
@@ -5454,18 +4755,14 @@
       <c r="F178" s="6">
         <v>50000000</v>
       </c>
-      <c r="G178" s="6">
-        <f t="shared" si="4"/>
-        <v>379978360</v>
+      <c r="G178" s="1">
+        <v>0</v>
       </c>
       <c r="H178" s="1">
         <v>0</v>
       </c>
-      <c r="I178" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="6"/>
       <c r="B179" s="1">
         <v>77</v>
@@ -5482,18 +4779,14 @@
       <c r="F179" s="6">
         <v>60000000</v>
       </c>
-      <c r="G179" s="6">
-        <f t="shared" si="4"/>
-        <v>439978360</v>
+      <c r="G179" s="1">
+        <v>0</v>
       </c>
       <c r="H179" s="1">
         <v>0</v>
       </c>
-      <c r="I179" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="6"/>
       <c r="B180" s="1">
         <v>78</v>
@@ -5510,18 +4803,14 @@
       <c r="F180" s="6">
         <v>65000000</v>
       </c>
-      <c r="G180" s="6">
-        <f t="shared" si="4"/>
-        <v>504978360</v>
+      <c r="G180" s="1">
+        <v>0</v>
       </c>
       <c r="H180" s="1">
         <v>0</v>
       </c>
-      <c r="I180" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="6"/>
       <c r="B181" s="1">
         <v>79</v>
@@ -5538,18 +4827,14 @@
       <c r="F181" s="6">
         <v>70000000</v>
       </c>
-      <c r="G181" s="6">
-        <f t="shared" si="4"/>
-        <v>574978360</v>
+      <c r="G181" s="1">
+        <v>0</v>
       </c>
       <c r="H181" s="1">
         <v>0</v>
       </c>
-      <c r="I181" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="6"/>
       <c r="B182" s="1">
         <v>80</v>
@@ -5566,18 +4851,14 @@
       <c r="F182" s="6">
         <v>75000000</v>
       </c>
-      <c r="G182" s="6">
-        <f t="shared" si="4"/>
-        <v>649978360</v>
+      <c r="G182" s="1">
+        <v>0</v>
       </c>
       <c r="H182" s="1">
         <v>0</v>
       </c>
-      <c r="I182" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="6"/>
       <c r="B183" s="1">
         <v>81</v>
@@ -5594,18 +4875,14 @@
       <c r="F183" s="6">
         <v>80000000</v>
       </c>
-      <c r="G183" s="6">
-        <f t="shared" si="4"/>
-        <v>729978360</v>
+      <c r="G183" s="1">
+        <v>0</v>
       </c>
       <c r="H183" s="1">
         <v>0</v>
       </c>
-      <c r="I183" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="6"/>
       <c r="B184" s="1">
         <v>82</v>
@@ -5622,18 +4899,14 @@
       <c r="F184" s="6">
         <v>90000000</v>
       </c>
-      <c r="G184" s="6">
-        <f t="shared" si="4"/>
-        <v>819978360</v>
+      <c r="G184" s="1">
+        <v>0</v>
       </c>
       <c r="H184" s="1">
         <v>0</v>
       </c>
-      <c r="I184" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="6"/>
       <c r="B185" s="1">
         <v>83</v>
@@ -5650,18 +4923,14 @@
       <c r="F185" s="6">
         <v>95000000</v>
       </c>
-      <c r="G185" s="6">
-        <f t="shared" si="4"/>
-        <v>914978360</v>
+      <c r="G185" s="1">
+        <v>0</v>
       </c>
       <c r="H185" s="1">
         <v>0</v>
       </c>
-      <c r="I185" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="6"/>
       <c r="B186" s="1">
         <v>84</v>
@@ -5678,18 +4947,14 @@
       <c r="F186" s="6">
         <v>100000000</v>
       </c>
-      <c r="G186" s="6">
-        <f t="shared" si="4"/>
-        <v>1014978360</v>
+      <c r="G186" s="1">
+        <v>0</v>
       </c>
       <c r="H186" s="1">
         <v>0</v>
       </c>
-      <c r="I186" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="6"/>
       <c r="B187" s="1">
         <v>85</v>
@@ -5706,18 +4971,14 @@
       <c r="F187" s="6">
         <v>105000000</v>
       </c>
-      <c r="G187" s="6">
-        <f t="shared" si="4"/>
-        <v>1119978360</v>
+      <c r="G187" s="1">
+        <v>0</v>
       </c>
       <c r="H187" s="1">
         <v>0</v>
       </c>
-      <c r="I187" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="6"/>
       <c r="B188" s="1">
         <v>86</v>
@@ -5734,18 +4995,14 @@
       <c r="F188" s="6">
         <v>110000000</v>
       </c>
-      <c r="G188" s="6">
-        <f t="shared" si="4"/>
-        <v>1229978360</v>
+      <c r="G188" s="1">
+        <v>0</v>
       </c>
       <c r="H188" s="1">
         <v>0</v>
       </c>
-      <c r="I188" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="6"/>
       <c r="B189" s="1">
         <v>87</v>
@@ -5762,18 +5019,14 @@
       <c r="F189" s="6">
         <v>110000000</v>
       </c>
-      <c r="G189" s="6">
-        <f t="shared" si="4"/>
-        <v>1339978360</v>
+      <c r="G189" s="1">
+        <v>0</v>
       </c>
       <c r="H189" s="1">
         <v>0</v>
       </c>
-      <c r="I189" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="6"/>
       <c r="B190" s="1">
         <v>88</v>
@@ -5790,18 +5043,14 @@
       <c r="F190" s="6">
         <v>120000000</v>
       </c>
-      <c r="G190" s="6">
-        <f t="shared" si="4"/>
-        <v>1459978360</v>
+      <c r="G190" s="1">
+        <v>0</v>
       </c>
       <c r="H190" s="1">
         <v>0</v>
       </c>
-      <c r="I190" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="6"/>
       <c r="B191" s="1">
         <v>89</v>
@@ -5818,18 +5067,14 @@
       <c r="F191" s="6">
         <v>120000000</v>
       </c>
-      <c r="G191" s="6">
-        <f t="shared" si="4"/>
-        <v>1579978360</v>
+      <c r="G191" s="1">
+        <v>0</v>
       </c>
       <c r="H191" s="1">
         <v>0</v>
       </c>
-      <c r="I191" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="6"/>
       <c r="B192" s="1">
         <v>90</v>
@@ -5846,18 +5091,14 @@
       <c r="F192" s="6">
         <v>30000000</v>
       </c>
-      <c r="G192" s="6">
-        <f t="shared" si="4"/>
-        <v>1609978360</v>
+      <c r="G192" s="1">
+        <v>0</v>
       </c>
       <c r="H192" s="1">
         <v>0</v>
       </c>
-      <c r="I192" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="6"/>
       <c r="B193" s="1">
         <v>91</v>
@@ -5874,18 +5115,14 @@
       <c r="F193" s="6">
         <v>130000000</v>
       </c>
-      <c r="G193" s="6">
-        <f t="shared" si="4"/>
-        <v>1739978360</v>
+      <c r="G193" s="1">
+        <v>0</v>
       </c>
       <c r="H193" s="1">
         <v>0</v>
       </c>
-      <c r="I193" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="6"/>
       <c r="B194" s="1">
         <v>92</v>
@@ -5902,18 +5139,14 @@
       <c r="F194" s="6">
         <v>150000000</v>
       </c>
-      <c r="G194" s="6">
-        <f t="shared" si="4"/>
-        <v>1889978360</v>
+      <c r="G194" s="1">
+        <v>0</v>
       </c>
       <c r="H194" s="1">
         <v>0</v>
       </c>
-      <c r="I194" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="6"/>
       <c r="B195" s="1">
         <v>93</v>
@@ -5930,18 +5163,14 @@
       <c r="F195" s="6">
         <v>160000000</v>
       </c>
-      <c r="G195" s="6">
-        <f t="shared" si="4"/>
-        <v>2049978360</v>
+      <c r="G195" s="1">
+        <v>0</v>
       </c>
       <c r="H195" s="1">
         <v>0</v>
       </c>
-      <c r="I195" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="6"/>
       <c r="B196" s="1">
         <v>94</v>
@@ -5958,18 +5187,14 @@
       <c r="F196" s="6">
         <v>160000000</v>
       </c>
-      <c r="G196" s="6">
-        <f t="shared" si="4"/>
-        <v>2209978360</v>
+      <c r="G196" s="1">
+        <v>0</v>
       </c>
       <c r="H196" s="1">
         <v>0</v>
       </c>
-      <c r="I196" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="6"/>
       <c r="B197" s="1">
         <v>95</v>
@@ -5986,18 +5211,14 @@
       <c r="F197" s="6">
         <v>170000000</v>
       </c>
-      <c r="G197" s="6">
-        <f t="shared" si="4"/>
-        <v>2379978360</v>
+      <c r="G197" s="1">
+        <v>0</v>
       </c>
       <c r="H197" s="1">
         <v>0</v>
       </c>
-      <c r="I197" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="6"/>
       <c r="B198" s="1">
         <v>96</v>
@@ -6014,18 +5235,14 @@
       <c r="F198" s="6">
         <v>190000000</v>
       </c>
-      <c r="G198" s="6">
-        <f t="shared" si="4"/>
-        <v>2569978360</v>
+      <c r="G198" s="1">
+        <v>0</v>
       </c>
       <c r="H198" s="1">
         <v>0</v>
       </c>
-      <c r="I198" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="6"/>
       <c r="B199" s="1">
         <v>97</v>
@@ -6042,18 +5259,14 @@
       <c r="F199" s="6">
         <v>200000000</v>
       </c>
-      <c r="G199" s="6">
-        <f t="shared" si="4"/>
-        <v>2769978360</v>
+      <c r="G199" s="1">
+        <v>0</v>
       </c>
       <c r="H199" s="1">
         <v>0</v>
       </c>
-      <c r="I199" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="6"/>
       <c r="B200" s="1">
         <v>98</v>
@@ -6070,18 +5283,14 @@
       <c r="F200" s="6">
         <v>200000000</v>
       </c>
-      <c r="G200" s="6">
-        <f t="shared" si="4"/>
-        <v>2969978360</v>
+      <c r="G200" s="1">
+        <v>0</v>
       </c>
       <c r="H200" s="1">
         <v>0</v>
       </c>
-      <c r="I200" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="6"/>
       <c r="B201" s="1">
         <v>99</v>
@@ -6098,20 +5307,16 @@
       <c r="F201" s="6">
         <v>0</v>
       </c>
-      <c r="G201" s="6">
-        <f t="shared" si="4"/>
-        <v>2969978360</v>
+      <c r="G201" s="1">
+        <v>0</v>
       </c>
       <c r="H201" s="1">
         <v>0</v>
       </c>
-      <c r="I201" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
@@ -6120,9 +5325,8 @@
       <c r="F202" s="6"/>
       <c r="G202" s="6"/>
       <c r="H202" s="6"/>
-      <c r="I202" s="6"/>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="6"/>
       <c r="B203" s="1">
         <v>5</v>
@@ -6139,18 +5343,14 @@
       <c r="F203" s="6">
         <v>900</v>
       </c>
-      <c r="G203" s="6">
-        <f>SUM(G9,F203)</f>
-        <v>2100</v>
+      <c r="G203" s="1">
+        <v>0</v>
       </c>
       <c r="H203" s="1">
         <v>0</v>
       </c>
-      <c r="I203" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="6"/>
       <c r="B204" s="1">
         <v>6</v>
@@ -6167,18 +5367,14 @@
       <c r="F204" s="6">
         <v>780</v>
       </c>
-      <c r="G204" s="6">
-        <f>SUM(G203,F204)</f>
-        <v>2880</v>
+      <c r="G204" s="1">
+        <v>0</v>
       </c>
       <c r="H204" s="1">
         <v>0</v>
       </c>
-      <c r="I204" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="6"/>
       <c r="B205" s="1">
         <v>7</v>
@@ -6195,18 +5391,14 @@
       <c r="F205" s="6">
         <v>960</v>
       </c>
-      <c r="G205" s="6">
-        <f t="shared" ref="G205:G268" si="5">SUM(G204,F205)</f>
-        <v>3840</v>
+      <c r="G205" s="1">
+        <v>0</v>
       </c>
       <c r="H205" s="1">
         <v>0</v>
       </c>
-      <c r="I205" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="6"/>
       <c r="B206" s="1">
         <v>8</v>
@@ -6223,18 +5415,14 @@
       <c r="F206" s="6">
         <v>1000</v>
       </c>
-      <c r="G206" s="6">
-        <f t="shared" si="5"/>
-        <v>4840</v>
+      <c r="G206" s="1">
+        <v>0</v>
       </c>
       <c r="H206" s="1">
         <v>0</v>
       </c>
-      <c r="I206" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="6"/>
       <c r="B207" s="1">
         <v>9</v>
@@ -6251,18 +5439,14 @@
       <c r="F207" s="6">
         <v>1920</v>
       </c>
-      <c r="G207" s="6">
-        <f t="shared" si="5"/>
-        <v>6760</v>
+      <c r="G207" s="1">
+        <v>0</v>
       </c>
       <c r="H207" s="1">
         <v>0</v>
       </c>
-      <c r="I207" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="6"/>
       <c r="B208" s="1">
         <v>10</v>
@@ -6279,18 +5463,14 @@
       <c r="F208" s="6">
         <v>1920</v>
       </c>
-      <c r="G208" s="6">
-        <f t="shared" si="5"/>
-        <v>8680</v>
+      <c r="G208" s="1">
+        <v>0</v>
       </c>
       <c r="H208" s="1">
         <v>0</v>
       </c>
-      <c r="I208" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="6"/>
       <c r="B209" s="1">
         <v>11</v>
@@ -6307,18 +5487,14 @@
       <c r="F209" s="6">
         <v>1920</v>
       </c>
-      <c r="G209" s="6">
-        <f t="shared" si="5"/>
-        <v>10600</v>
+      <c r="G209" s="1">
+        <v>0</v>
       </c>
       <c r="H209" s="1">
         <v>0</v>
       </c>
-      <c r="I209" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="6"/>
       <c r="B210" s="1">
         <v>12</v>
@@ -6335,18 +5511,14 @@
       <c r="F210" s="6">
         <v>3840</v>
       </c>
-      <c r="G210" s="6">
-        <f t="shared" si="5"/>
-        <v>14440</v>
+      <c r="G210" s="1">
+        <v>0</v>
       </c>
       <c r="H210" s="1">
         <v>0</v>
       </c>
-      <c r="I210" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="6"/>
       <c r="B211" s="1">
         <v>13</v>
@@ -6363,18 +5535,14 @@
       <c r="F211" s="6">
         <v>3840</v>
       </c>
-      <c r="G211" s="6">
-        <f t="shared" si="5"/>
-        <v>18280</v>
+      <c r="G211" s="1">
+        <v>0</v>
       </c>
       <c r="H211" s="1">
         <v>0</v>
       </c>
-      <c r="I211" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="6"/>
       <c r="B212" s="1">
         <v>14</v>
@@ -6391,18 +5559,14 @@
       <c r="F212" s="6">
         <v>3840</v>
       </c>
-      <c r="G212" s="6">
-        <f t="shared" si="5"/>
-        <v>22120</v>
+      <c r="G212" s="1">
+        <v>0</v>
       </c>
       <c r="H212" s="1">
         <v>0</v>
       </c>
-      <c r="I212" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="6"/>
       <c r="B213" s="1">
         <v>15</v>
@@ -6419,18 +5583,14 @@
       <c r="F213" s="6">
         <v>7680</v>
       </c>
-      <c r="G213" s="6">
-        <f t="shared" si="5"/>
-        <v>29800</v>
+      <c r="G213" s="1">
+        <v>0</v>
       </c>
       <c r="H213" s="1">
         <v>0</v>
       </c>
-      <c r="I213" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="6"/>
       <c r="B214" s="1">
         <v>16</v>
@@ -6447,18 +5607,14 @@
       <c r="F214" s="6">
         <v>7680</v>
       </c>
-      <c r="G214" s="6">
-        <f t="shared" si="5"/>
-        <v>37480</v>
+      <c r="G214" s="1">
+        <v>0</v>
       </c>
       <c r="H214" s="1">
         <v>0</v>
       </c>
-      <c r="I214" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="6"/>
       <c r="B215" s="1">
         <v>17</v>
@@ -6475,18 +5631,14 @@
       <c r="F215" s="6">
         <v>7680</v>
       </c>
-      <c r="G215" s="6">
-        <f t="shared" si="5"/>
-        <v>45160</v>
+      <c r="G215" s="1">
+        <v>0</v>
       </c>
       <c r="H215" s="1">
         <v>0</v>
       </c>
-      <c r="I215" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="6"/>
       <c r="B216" s="1">
         <v>18</v>
@@ -6503,18 +5655,14 @@
       <c r="F216" s="6">
         <v>15360</v>
       </c>
-      <c r="G216" s="6">
-        <f t="shared" si="5"/>
-        <v>60520</v>
+      <c r="G216" s="1">
+        <v>0</v>
       </c>
       <c r="H216" s="1">
         <v>0</v>
       </c>
-      <c r="I216" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="6"/>
       <c r="B217" s="1">
         <v>19</v>
@@ -6531,18 +5679,14 @@
       <c r="F217" s="6">
         <v>15360</v>
       </c>
-      <c r="G217" s="6">
-        <f t="shared" si="5"/>
-        <v>75880</v>
+      <c r="G217" s="1">
+        <v>0</v>
       </c>
       <c r="H217" s="1">
         <v>0</v>
       </c>
-      <c r="I217" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="6"/>
       <c r="B218" s="1">
         <v>20</v>
@@ -6559,18 +5703,14 @@
       <c r="F218" s="6">
         <v>15360</v>
       </c>
-      <c r="G218" s="6">
-        <f t="shared" si="5"/>
-        <v>91240</v>
+      <c r="G218" s="1">
+        <v>0</v>
       </c>
       <c r="H218" s="1">
         <v>0</v>
       </c>
-      <c r="I218" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="6"/>
       <c r="B219" s="1">
         <v>21</v>
@@ -6587,18 +5727,14 @@
       <c r="F219" s="6">
         <v>30720</v>
       </c>
-      <c r="G219" s="6">
-        <f t="shared" si="5"/>
-        <v>121960</v>
+      <c r="G219" s="1">
+        <v>0</v>
       </c>
       <c r="H219" s="1">
         <v>0</v>
       </c>
-      <c r="I219" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="6"/>
       <c r="B220" s="1">
         <v>22</v>
@@ -6615,18 +5751,14 @@
       <c r="F220" s="6">
         <v>30720</v>
       </c>
-      <c r="G220" s="6">
-        <f t="shared" si="5"/>
-        <v>152680</v>
+      <c r="G220" s="1">
+        <v>0</v>
       </c>
       <c r="H220" s="1">
         <v>0</v>
       </c>
-      <c r="I220" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="6"/>
       <c r="B221" s="1">
         <v>23</v>
@@ -6643,18 +5775,14 @@
       <c r="F221" s="6">
         <v>30720</v>
       </c>
-      <c r="G221" s="6">
-        <f t="shared" si="5"/>
-        <v>183400</v>
+      <c r="G221" s="1">
+        <v>0</v>
       </c>
       <c r="H221" s="1">
         <v>0</v>
       </c>
-      <c r="I221" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="6"/>
       <c r="B222" s="1">
         <v>24</v>
@@ -6671,18 +5799,14 @@
       <c r="F222" s="6">
         <v>61440</v>
       </c>
-      <c r="G222" s="6">
-        <f t="shared" si="5"/>
-        <v>244840</v>
+      <c r="G222" s="1">
+        <v>0</v>
       </c>
       <c r="H222" s="1">
         <v>0</v>
       </c>
-      <c r="I222" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="6"/>
       <c r="B223" s="1">
         <v>25</v>
@@ -6699,18 +5823,14 @@
       <c r="F223" s="6">
         <v>61440</v>
       </c>
-      <c r="G223" s="6">
-        <f t="shared" si="5"/>
-        <v>306280</v>
+      <c r="G223" s="1">
+        <v>0</v>
       </c>
       <c r="H223" s="1">
         <v>0</v>
       </c>
-      <c r="I223" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="6"/>
       <c r="B224" s="1">
         <v>26</v>
@@ -6727,18 +5847,14 @@
       <c r="F224" s="6">
         <v>61440</v>
       </c>
-      <c r="G224" s="6">
-        <f t="shared" si="5"/>
-        <v>367720</v>
+      <c r="G224" s="1">
+        <v>0</v>
       </c>
       <c r="H224" s="1">
         <v>0</v>
       </c>
-      <c r="I224" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="6"/>
       <c r="B225" s="1">
         <v>27</v>
@@ -6755,18 +5871,14 @@
       <c r="F225" s="6">
         <v>122880</v>
       </c>
-      <c r="G225" s="6">
-        <f t="shared" si="5"/>
-        <v>490600</v>
+      <c r="G225" s="1">
+        <v>0</v>
       </c>
       <c r="H225" s="1">
         <v>0</v>
       </c>
-      <c r="I225" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="6"/>
       <c r="B226" s="1">
         <v>28</v>
@@ -6783,18 +5895,14 @@
       <c r="F226" s="6">
         <v>122880</v>
       </c>
-      <c r="G226" s="6">
-        <f t="shared" si="5"/>
-        <v>613480</v>
+      <c r="G226" s="1">
+        <v>0</v>
       </c>
       <c r="H226" s="1">
         <v>0</v>
       </c>
-      <c r="I226" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="6"/>
       <c r="B227" s="1">
         <v>29</v>
@@ -6811,18 +5919,14 @@
       <c r="F227" s="6">
         <v>122880</v>
       </c>
-      <c r="G227" s="6">
-        <f t="shared" si="5"/>
-        <v>736360</v>
+      <c r="G227" s="1">
+        <v>0</v>
       </c>
       <c r="H227" s="1">
         <v>0</v>
       </c>
-      <c r="I227" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="6"/>
       <c r="B228" s="1">
         <v>30</v>
@@ -6839,18 +5943,14 @@
       <c r="F228" s="6">
         <v>180000</v>
       </c>
-      <c r="G228" s="6">
-        <f t="shared" si="5"/>
-        <v>916360</v>
+      <c r="G228" s="1">
+        <v>0</v>
       </c>
       <c r="H228" s="1">
         <v>0</v>
       </c>
-      <c r="I228" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="6"/>
       <c r="B229" s="1">
         <v>31</v>
@@ -6867,18 +5967,14 @@
       <c r="F229" s="6">
         <v>180000</v>
       </c>
-      <c r="G229" s="6">
-        <f t="shared" si="5"/>
-        <v>1096360</v>
+      <c r="G229" s="1">
+        <v>0</v>
       </c>
       <c r="H229" s="1">
         <v>0</v>
       </c>
-      <c r="I229" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="6"/>
       <c r="B230" s="1">
         <v>32</v>
@@ -6895,18 +5991,14 @@
       <c r="F230" s="6">
         <v>180000</v>
       </c>
-      <c r="G230" s="6">
-        <f t="shared" si="5"/>
-        <v>1276360</v>
+      <c r="G230" s="1">
+        <v>0</v>
       </c>
       <c r="H230" s="1">
         <v>0</v>
       </c>
-      <c r="I230" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="6"/>
       <c r="B231" s="1">
         <v>33</v>
@@ -6923,18 +6015,14 @@
       <c r="F231" s="6">
         <v>250000</v>
       </c>
-      <c r="G231" s="6">
-        <f t="shared" si="5"/>
-        <v>1526360</v>
+      <c r="G231" s="1">
+        <v>0</v>
       </c>
       <c r="H231" s="1">
         <v>0</v>
       </c>
-      <c r="I231" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="6"/>
       <c r="B232" s="1">
         <v>34</v>
@@ -6951,18 +6039,14 @@
       <c r="F232" s="6">
         <v>250000</v>
       </c>
-      <c r="G232" s="6">
-        <f t="shared" si="5"/>
-        <v>1776360</v>
+      <c r="G232" s="1">
+        <v>0</v>
       </c>
       <c r="H232" s="1">
         <v>0</v>
       </c>
-      <c r="I232" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="6"/>
       <c r="B233" s="1">
         <v>35</v>
@@ -6979,18 +6063,14 @@
       <c r="F233" s="6">
         <v>250000</v>
       </c>
-      <c r="G233" s="6">
-        <f t="shared" si="5"/>
-        <v>2026360</v>
+      <c r="G233" s="1">
+        <v>0</v>
       </c>
       <c r="H233" s="1">
         <v>0</v>
       </c>
-      <c r="I233" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="6"/>
       <c r="B234" s="1">
         <v>36</v>
@@ -7007,18 +6087,14 @@
       <c r="F234" s="6">
         <v>360000</v>
       </c>
-      <c r="G234" s="6">
-        <f t="shared" si="5"/>
-        <v>2386360</v>
+      <c r="G234" s="1">
+        <v>0</v>
       </c>
       <c r="H234" s="1">
         <v>0</v>
       </c>
-      <c r="I234" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="6"/>
       <c r="B235" s="1">
         <v>37</v>
@@ -7035,18 +6111,14 @@
       <c r="F235" s="6">
         <v>360000</v>
       </c>
-      <c r="G235" s="6">
-        <f t="shared" si="5"/>
-        <v>2746360</v>
+      <c r="G235" s="1">
+        <v>0</v>
       </c>
       <c r="H235" s="1">
         <v>0</v>
       </c>
-      <c r="I235" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="6"/>
       <c r="B236" s="1">
         <v>38</v>
@@ -7063,18 +6135,14 @@
       <c r="F236" s="6">
         <v>360000</v>
       </c>
-      <c r="G236" s="6">
-        <f t="shared" si="5"/>
-        <v>3106360</v>
+      <c r="G236" s="1">
+        <v>0</v>
       </c>
       <c r="H236" s="1">
         <v>0</v>
       </c>
-      <c r="I236" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="6"/>
       <c r="B237" s="1">
         <v>39</v>
@@ -7091,18 +6159,14 @@
       <c r="F237" s="6">
         <v>390000</v>
       </c>
-      <c r="G237" s="6">
-        <f t="shared" si="5"/>
-        <v>3496360</v>
+      <c r="G237" s="1">
+        <v>0</v>
       </c>
       <c r="H237" s="1">
         <v>0</v>
       </c>
-      <c r="I237" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="6"/>
       <c r="B238" s="1">
         <v>40</v>
@@ -7119,18 +6183,14 @@
       <c r="F238" s="6">
         <v>390000</v>
       </c>
-      <c r="G238" s="6">
-        <f t="shared" si="5"/>
-        <v>3886360</v>
+      <c r="G238" s="1">
+        <v>0</v>
       </c>
       <c r="H238" s="1">
         <v>0</v>
       </c>
-      <c r="I238" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="6"/>
       <c r="B239" s="1">
         <v>41</v>
@@ -7147,18 +6207,14 @@
       <c r="F239" s="6">
         <v>390000</v>
       </c>
-      <c r="G239" s="6">
-        <f t="shared" si="5"/>
-        <v>4276360</v>
+      <c r="G239" s="1">
+        <v>0</v>
       </c>
       <c r="H239" s="1">
         <v>0</v>
       </c>
-      <c r="I239" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="6"/>
       <c r="B240" s="1">
         <v>42</v>
@@ -7175,18 +6231,14 @@
       <c r="F240" s="6">
         <v>580000</v>
       </c>
-      <c r="G240" s="6">
-        <f t="shared" si="5"/>
-        <v>4856360</v>
+      <c r="G240" s="1">
+        <v>0</v>
       </c>
       <c r="H240" s="1">
         <v>0</v>
       </c>
-      <c r="I240" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="6"/>
       <c r="B241" s="1">
         <v>43</v>
@@ -7203,18 +6255,14 @@
       <c r="F241" s="6">
         <v>580000</v>
       </c>
-      <c r="G241" s="6">
-        <f t="shared" si="5"/>
-        <v>5436360</v>
+      <c r="G241" s="1">
+        <v>0</v>
       </c>
       <c r="H241" s="1">
         <v>0</v>
       </c>
-      <c r="I241" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="6"/>
       <c r="B242" s="1">
         <v>44</v>
@@ -7231,18 +6279,14 @@
       <c r="F242" s="6">
         <v>580000</v>
       </c>
-      <c r="G242" s="6">
-        <f t="shared" si="5"/>
-        <v>6016360</v>
+      <c r="G242" s="1">
+        <v>0</v>
       </c>
       <c r="H242" s="1">
         <v>0</v>
       </c>
-      <c r="I242" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="6"/>
       <c r="B243" s="1">
         <v>45</v>
@@ -7259,18 +6303,14 @@
       <c r="F243" s="6">
         <v>780000</v>
       </c>
-      <c r="G243" s="6">
-        <f t="shared" si="5"/>
-        <v>6796360</v>
+      <c r="G243" s="1">
+        <v>0</v>
       </c>
       <c r="H243" s="1">
         <v>0</v>
       </c>
-      <c r="I243" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="6"/>
       <c r="B244" s="1">
         <v>46</v>
@@ -7287,18 +6327,14 @@
       <c r="F244" s="6">
         <v>780000</v>
       </c>
-      <c r="G244" s="6">
-        <f t="shared" si="5"/>
-        <v>7576360</v>
+      <c r="G244" s="1">
+        <v>0</v>
       </c>
       <c r="H244" s="1">
         <v>0</v>
       </c>
-      <c r="I244" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="6"/>
       <c r="B245" s="1">
         <v>47</v>
@@ -7315,18 +6351,14 @@
       <c r="F245" s="6">
         <v>780000</v>
       </c>
-      <c r="G245" s="6">
-        <f t="shared" si="5"/>
-        <v>8356360</v>
+      <c r="G245" s="1">
+        <v>0</v>
       </c>
       <c r="H245" s="1">
         <v>0</v>
       </c>
-      <c r="I245" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="6"/>
       <c r="B246" s="1">
         <v>48</v>
@@ -7343,18 +6375,14 @@
       <c r="F246" s="6">
         <v>1150000</v>
       </c>
-      <c r="G246" s="6">
-        <f t="shared" si="5"/>
-        <v>9506360</v>
+      <c r="G246" s="1">
+        <v>0</v>
       </c>
       <c r="H246" s="1">
         <v>0</v>
       </c>
-      <c r="I246" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="6"/>
       <c r="B247" s="1">
         <v>49</v>
@@ -7371,18 +6399,14 @@
       <c r="F247" s="6">
         <v>1150000</v>
       </c>
-      <c r="G247" s="6">
-        <f t="shared" si="5"/>
-        <v>10656360</v>
+      <c r="G247" s="1">
+        <v>0</v>
       </c>
       <c r="H247" s="1">
         <v>0</v>
       </c>
-      <c r="I247" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="6"/>
       <c r="B248" s="1">
         <v>50</v>
@@ -7399,18 +6423,14 @@
       <c r="F248" s="6">
         <v>1150000</v>
       </c>
-      <c r="G248" s="6">
-        <f t="shared" si="5"/>
-        <v>11806360</v>
+      <c r="G248" s="1">
+        <v>0</v>
       </c>
       <c r="H248" s="1">
         <v>0</v>
       </c>
-      <c r="I248" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="6"/>
       <c r="B249" s="1">
         <v>51</v>
@@ -7427,18 +6447,14 @@
       <c r="F249" s="6">
         <v>1310000</v>
       </c>
-      <c r="G249" s="6">
-        <f t="shared" si="5"/>
-        <v>13116360</v>
+      <c r="G249" s="1">
+        <v>0</v>
       </c>
       <c r="H249" s="1">
         <v>0</v>
       </c>
-      <c r="I249" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="6"/>
       <c r="B250" s="1">
         <v>52</v>
@@ -7455,18 +6471,14 @@
       <c r="F250" s="6">
         <v>1310000</v>
       </c>
-      <c r="G250" s="6">
-        <f t="shared" si="5"/>
-        <v>14426360</v>
+      <c r="G250" s="1">
+        <v>0</v>
       </c>
       <c r="H250" s="1">
         <v>0</v>
       </c>
-      <c r="I250" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="6"/>
       <c r="B251" s="1">
         <v>53</v>
@@ -7483,18 +6495,14 @@
       <c r="F251" s="6">
         <v>1310000</v>
       </c>
-      <c r="G251" s="6">
-        <f t="shared" si="5"/>
-        <v>15736360</v>
+      <c r="G251" s="1">
+        <v>0</v>
       </c>
       <c r="H251" s="1">
         <v>0</v>
       </c>
-      <c r="I251" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="6"/>
       <c r="B252" s="1">
         <v>54</v>
@@ -7511,18 +6519,14 @@
       <c r="F252" s="6">
         <v>1920000</v>
       </c>
-      <c r="G252" s="6">
-        <f t="shared" si="5"/>
-        <v>17656360</v>
+      <c r="G252" s="1">
+        <v>0</v>
       </c>
       <c r="H252" s="1">
         <v>0</v>
       </c>
-      <c r="I252" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="6"/>
       <c r="B253" s="1">
         <v>55</v>
@@ -7539,18 +6543,14 @@
       <c r="F253" s="6">
         <v>1920000</v>
       </c>
-      <c r="G253" s="6">
-        <f t="shared" si="5"/>
-        <v>19576360</v>
+      <c r="G253" s="1">
+        <v>0</v>
       </c>
       <c r="H253" s="1">
         <v>0</v>
       </c>
-      <c r="I253" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="6"/>
       <c r="B254" s="1">
         <v>56</v>
@@ -7567,18 +6567,14 @@
       <c r="F254" s="6">
         <v>1920000</v>
       </c>
-      <c r="G254" s="6">
-        <f t="shared" si="5"/>
-        <v>21496360</v>
+      <c r="G254" s="1">
+        <v>0</v>
       </c>
       <c r="H254" s="1">
         <v>0</v>
       </c>
-      <c r="I254" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="6"/>
       <c r="B255" s="1">
         <v>57</v>
@@ -7595,18 +6591,14 @@
       <c r="F255" s="6">
         <v>4200000</v>
       </c>
-      <c r="G255" s="6">
-        <f t="shared" si="5"/>
-        <v>25696360</v>
+      <c r="G255" s="1">
+        <v>0</v>
       </c>
       <c r="H255" s="1">
         <v>0</v>
       </c>
-      <c r="I255" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="6"/>
       <c r="B256" s="1">
         <v>58</v>
@@ -7623,18 +6615,14 @@
       <c r="F256" s="6">
         <v>4200000</v>
       </c>
-      <c r="G256" s="6">
-        <f t="shared" si="5"/>
-        <v>29896360</v>
+      <c r="G256" s="1">
+        <v>0</v>
       </c>
       <c r="H256" s="1">
         <v>0</v>
       </c>
-      <c r="I256" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="6"/>
       <c r="B257" s="1">
         <v>59</v>
@@ -7651,18 +6639,14 @@
       <c r="F257" s="6">
         <v>4200000</v>
       </c>
-      <c r="G257" s="6">
-        <f t="shared" si="5"/>
-        <v>34096360</v>
+      <c r="G257" s="1">
+        <v>0</v>
       </c>
       <c r="H257" s="1">
         <v>0</v>
       </c>
-      <c r="I257" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="6"/>
       <c r="B258" s="1">
         <v>60</v>
@@ -7679,18 +6663,14 @@
       <c r="F258" s="6">
         <v>5120000</v>
       </c>
-      <c r="G258" s="6">
-        <f t="shared" si="5"/>
-        <v>39216360</v>
+      <c r="G258" s="1">
+        <v>0</v>
       </c>
       <c r="H258" s="1">
         <v>0</v>
       </c>
-      <c r="I258" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="6"/>
       <c r="B259" s="1">
         <v>61</v>
@@ -7707,18 +6687,14 @@
       <c r="F259" s="6">
         <v>5120000</v>
       </c>
-      <c r="G259" s="6">
-        <f t="shared" si="5"/>
-        <v>44336360</v>
+      <c r="G259" s="1">
+        <v>0</v>
       </c>
       <c r="H259" s="1">
         <v>0</v>
       </c>
-      <c r="I259" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="6"/>
       <c r="B260" s="1">
         <v>62</v>
@@ -7735,18 +6711,14 @@
       <c r="F260" s="6">
         <v>5120000</v>
       </c>
-      <c r="G260" s="6">
-        <f t="shared" si="5"/>
-        <v>49456360</v>
+      <c r="G260" s="1">
+        <v>0</v>
       </c>
       <c r="H260" s="1">
         <v>0</v>
       </c>
-      <c r="I260" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="6"/>
       <c r="B261" s="1">
         <v>63</v>
@@ -7763,18 +6735,14 @@
       <c r="F261" s="6">
         <v>7980000</v>
       </c>
-      <c r="G261" s="6">
-        <f t="shared" si="5"/>
-        <v>57436360</v>
+      <c r="G261" s="1">
+        <v>0</v>
       </c>
       <c r="H261" s="1">
         <v>0</v>
       </c>
-      <c r="I261" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="6"/>
       <c r="B262" s="1">
         <v>64</v>
@@ -7791,18 +6759,14 @@
       <c r="F262" s="6">
         <v>7980000</v>
       </c>
-      <c r="G262" s="6">
-        <f t="shared" si="5"/>
-        <v>65416360</v>
+      <c r="G262" s="1">
+        <v>0</v>
       </c>
       <c r="H262" s="1">
         <v>0</v>
       </c>
-      <c r="I262" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="6"/>
       <c r="B263" s="1">
         <v>65</v>
@@ -7819,18 +6783,14 @@
       <c r="F263" s="6">
         <v>7980000</v>
       </c>
-      <c r="G263" s="6">
-        <f t="shared" si="5"/>
-        <v>73396360</v>
+      <c r="G263" s="1">
+        <v>0</v>
       </c>
       <c r="H263" s="1">
         <v>0</v>
       </c>
-      <c r="I263" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="6"/>
       <c r="B264" s="1">
         <v>66</v>
@@ -7847,18 +6807,14 @@
       <c r="F264" s="6">
         <v>8660000</v>
       </c>
-      <c r="G264" s="6">
-        <f t="shared" si="5"/>
-        <v>82056360</v>
+      <c r="G264" s="1">
+        <v>0</v>
       </c>
       <c r="H264" s="1">
         <v>0</v>
       </c>
-      <c r="I264" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="6"/>
       <c r="B265" s="1">
         <v>67</v>
@@ -7875,18 +6831,14 @@
       <c r="F265" s="6">
         <v>8660000</v>
       </c>
-      <c r="G265" s="6">
-        <f t="shared" si="5"/>
-        <v>90716360</v>
+      <c r="G265" s="1">
+        <v>0</v>
       </c>
       <c r="H265" s="1">
         <v>0</v>
       </c>
-      <c r="I265" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="6"/>
       <c r="B266" s="1">
         <v>68</v>
@@ -7903,18 +6855,14 @@
       <c r="F266" s="6">
         <v>8660000</v>
       </c>
-      <c r="G266" s="6">
-        <f t="shared" si="5"/>
-        <v>99376360</v>
+      <c r="G266" s="1">
+        <v>0</v>
       </c>
       <c r="H266" s="1">
         <v>0</v>
       </c>
-      <c r="I266" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="6"/>
       <c r="B267" s="1">
         <v>69</v>
@@ -7931,18 +6879,14 @@
       <c r="F267" s="6">
         <v>1700000</v>
       </c>
-      <c r="G267" s="6">
-        <f t="shared" si="5"/>
-        <v>101076360</v>
+      <c r="G267" s="1">
+        <v>0</v>
       </c>
       <c r="H267" s="1">
         <v>0</v>
       </c>
-      <c r="I267" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="6"/>
       <c r="B268" s="1">
         <v>70</v>
@@ -7959,18 +6903,14 @@
       <c r="F268" s="6">
         <v>20000000</v>
       </c>
-      <c r="G268" s="6">
-        <f t="shared" si="5"/>
-        <v>121076360</v>
+      <c r="G268" s="1">
+        <v>0</v>
       </c>
       <c r="H268" s="1">
         <v>0</v>
       </c>
-      <c r="I268" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="6"/>
       <c r="B269" s="1">
         <v>71</v>
@@ -7987,18 +6927,14 @@
       <c r="F269" s="6">
         <v>10000000</v>
       </c>
-      <c r="G269" s="6">
-        <f t="shared" ref="G269:G297" si="6">SUM(G268,F269)</f>
-        <v>131076360</v>
+      <c r="G269" s="1">
+        <v>0</v>
       </c>
       <c r="H269" s="1">
         <v>0</v>
       </c>
-      <c r="I269" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="6"/>
       <c r="B270" s="1">
         <v>72</v>
@@ -8015,18 +6951,14 @@
       <c r="F270" s="6">
         <v>10000000</v>
       </c>
-      <c r="G270" s="6">
-        <f t="shared" si="6"/>
-        <v>141076360</v>
+      <c r="G270" s="1">
+        <v>0</v>
       </c>
       <c r="H270" s="1">
         <v>0</v>
       </c>
-      <c r="I270" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="6"/>
       <c r="B271" s="1">
         <v>73</v>
@@ -8043,18 +6975,14 @@
       <c r="F271" s="6">
         <v>10000000</v>
       </c>
-      <c r="G271" s="6">
-        <f t="shared" si="6"/>
-        <v>151076360</v>
+      <c r="G271" s="1">
+        <v>0</v>
       </c>
       <c r="H271" s="1">
         <v>0</v>
       </c>
-      <c r="I271" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="6"/>
       <c r="B272" s="1">
         <v>74</v>
@@ -8071,18 +6999,14 @@
       <c r="F272" s="6">
         <v>10000000</v>
       </c>
-      <c r="G272" s="6">
-        <f t="shared" si="6"/>
-        <v>161076360</v>
+      <c r="G272" s="1">
+        <v>0</v>
       </c>
       <c r="H272" s="1">
         <v>0</v>
       </c>
-      <c r="I272" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="6"/>
       <c r="B273" s="1">
         <v>75</v>
@@ -8099,18 +7023,14 @@
       <c r="F273" s="6">
         <v>20000000</v>
       </c>
-      <c r="G273" s="6">
-        <f t="shared" si="6"/>
-        <v>181076360</v>
+      <c r="G273" s="1">
+        <v>0</v>
       </c>
       <c r="H273" s="1">
         <v>0</v>
       </c>
-      <c r="I273" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="6"/>
       <c r="B274" s="1">
         <v>76</v>
@@ -8127,18 +7047,14 @@
       <c r="F274" s="6">
         <v>20000000</v>
       </c>
-      <c r="G274" s="6">
-        <f t="shared" si="6"/>
-        <v>201076360</v>
+      <c r="G274" s="1">
+        <v>0</v>
       </c>
       <c r="H274" s="1">
         <v>0</v>
       </c>
-      <c r="I274" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="6"/>
       <c r="B275" s="1">
         <v>77</v>
@@ -8155,18 +7071,14 @@
       <c r="F275" s="6">
         <v>30000000</v>
       </c>
-      <c r="G275" s="6">
-        <f t="shared" si="6"/>
-        <v>231076360</v>
+      <c r="G275" s="1">
+        <v>0</v>
       </c>
       <c r="H275" s="1">
         <v>0</v>
       </c>
-      <c r="I275" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="6"/>
       <c r="B276" s="1">
         <v>78</v>
@@ -8183,18 +7095,14 @@
       <c r="F276" s="6">
         <v>20000000</v>
       </c>
-      <c r="G276" s="6">
-        <f t="shared" si="6"/>
-        <v>251076360</v>
+      <c r="G276" s="1">
+        <v>0</v>
       </c>
       <c r="H276" s="1">
         <v>0</v>
       </c>
-      <c r="I276" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="6"/>
       <c r="B277" s="1">
         <v>79</v>
@@ -8211,18 +7119,14 @@
       <c r="F277" s="6">
         <v>30000000</v>
       </c>
-      <c r="G277" s="6">
-        <f t="shared" si="6"/>
-        <v>281076360</v>
+      <c r="G277" s="1">
+        <v>0</v>
       </c>
       <c r="H277" s="1">
         <v>0</v>
       </c>
-      <c r="I277" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="6"/>
       <c r="B278" s="1">
         <v>80</v>
@@ -8239,18 +7143,14 @@
       <c r="F278" s="6">
         <v>30000000</v>
       </c>
-      <c r="G278" s="6">
-        <f t="shared" si="6"/>
-        <v>311076360</v>
+      <c r="G278" s="1">
+        <v>0</v>
       </c>
       <c r="H278" s="1">
         <v>0</v>
       </c>
-      <c r="I278" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" s="6"/>
       <c r="B279" s="1">
         <v>81</v>
@@ -8267,18 +7167,14 @@
       <c r="F279" s="6">
         <v>40000000</v>
       </c>
-      <c r="G279" s="6">
-        <f t="shared" si="6"/>
-        <v>351076360</v>
+      <c r="G279" s="1">
+        <v>0</v>
       </c>
       <c r="H279" s="1">
         <v>0</v>
       </c>
-      <c r="I279" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" s="6"/>
       <c r="B280" s="1">
         <v>82</v>
@@ -8295,18 +7191,14 @@
       <c r="F280" s="6">
         <v>40000000</v>
       </c>
-      <c r="G280" s="6">
-        <f t="shared" si="6"/>
-        <v>391076360</v>
+      <c r="G280" s="1">
+        <v>0</v>
       </c>
       <c r="H280" s="1">
         <v>0</v>
       </c>
-      <c r="I280" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" s="6"/>
       <c r="B281" s="1">
         <v>83</v>
@@ -8323,18 +7215,14 @@
       <c r="F281" s="6">
         <v>40000000</v>
       </c>
-      <c r="G281" s="6">
-        <f t="shared" si="6"/>
-        <v>431076360</v>
+      <c r="G281" s="1">
+        <v>0</v>
       </c>
       <c r="H281" s="1">
         <v>0</v>
       </c>
-      <c r="I281" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" s="6"/>
       <c r="B282" s="1">
         <v>84</v>
@@ -8351,18 +7239,14 @@
       <c r="F282" s="6">
         <v>40000000</v>
       </c>
-      <c r="G282" s="6">
-        <f t="shared" si="6"/>
-        <v>471076360</v>
+      <c r="G282" s="1">
+        <v>0</v>
       </c>
       <c r="H282" s="1">
         <v>0</v>
       </c>
-      <c r="I282" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" s="6"/>
       <c r="B283" s="1">
         <v>85</v>
@@ -8379,18 +7263,14 @@
       <c r="F283" s="6">
         <v>50000000</v>
       </c>
-      <c r="G283" s="6">
-        <f t="shared" si="6"/>
-        <v>521076360</v>
+      <c r="G283" s="1">
+        <v>0</v>
       </c>
       <c r="H283" s="1">
         <v>0</v>
       </c>
-      <c r="I283" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" s="6"/>
       <c r="B284" s="1">
         <v>86</v>
@@ -8407,18 +7287,14 @@
       <c r="F284" s="6">
         <v>50000000</v>
       </c>
-      <c r="G284" s="6">
-        <f t="shared" si="6"/>
-        <v>571076360</v>
+      <c r="G284" s="1">
+        <v>0</v>
       </c>
       <c r="H284" s="1">
         <v>0</v>
       </c>
-      <c r="I284" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" s="6"/>
       <c r="B285" s="1">
         <v>87</v>
@@ -8435,18 +7311,14 @@
       <c r="F285" s="6">
         <v>60000000</v>
       </c>
-      <c r="G285" s="6">
-        <f t="shared" si="6"/>
-        <v>631076360</v>
+      <c r="G285" s="1">
+        <v>0</v>
       </c>
       <c r="H285" s="1">
         <v>0</v>
       </c>
-      <c r="I285" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" s="6"/>
       <c r="B286" s="1">
         <v>88</v>
@@ -8463,18 +7335,14 @@
       <c r="F286" s="6">
         <v>60000000</v>
       </c>
-      <c r="G286" s="6">
-        <f t="shared" si="6"/>
-        <v>691076360</v>
+      <c r="G286" s="1">
+        <v>0</v>
       </c>
       <c r="H286" s="1">
         <v>0</v>
       </c>
-      <c r="I286" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" s="6"/>
       <c r="B287" s="1">
         <v>89</v>
@@ -8491,18 +7359,14 @@
       <c r="F287" s="6">
         <v>70000000</v>
       </c>
-      <c r="G287" s="6">
-        <f t="shared" si="6"/>
-        <v>761076360</v>
+      <c r="G287" s="1">
+        <v>0</v>
       </c>
       <c r="H287" s="1">
         <v>0</v>
       </c>
-      <c r="I287" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" s="6"/>
       <c r="B288" s="1">
         <v>90</v>
@@ -8519,18 +7383,14 @@
       <c r="F288" s="6">
         <v>80000000</v>
       </c>
-      <c r="G288" s="6">
-        <f t="shared" si="6"/>
-        <v>841076360</v>
+      <c r="G288" s="1">
+        <v>0</v>
       </c>
       <c r="H288" s="1">
         <v>0</v>
       </c>
-      <c r="I288" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" s="6"/>
       <c r="B289" s="1">
         <v>91</v>
@@ -8547,18 +7407,14 @@
       <c r="F289" s="6">
         <v>90000000</v>
       </c>
-      <c r="G289" s="6">
-        <f t="shared" si="6"/>
-        <v>931076360</v>
+      <c r="G289" s="1">
+        <v>0</v>
       </c>
       <c r="H289" s="1">
         <v>0</v>
       </c>
-      <c r="I289" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" s="6"/>
       <c r="B290" s="1">
         <v>92</v>
@@ -8575,18 +7431,14 @@
       <c r="F290" s="6">
         <v>100000000</v>
       </c>
-      <c r="G290" s="6">
-        <f t="shared" si="6"/>
-        <v>1031076360</v>
+      <c r="G290" s="1">
+        <v>0</v>
       </c>
       <c r="H290" s="1">
         <v>0</v>
       </c>
-      <c r="I290" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" s="6"/>
       <c r="B291" s="1">
         <v>93</v>
@@ -8603,18 +7455,14 @@
       <c r="F291" s="6">
         <v>90000000</v>
       </c>
-      <c r="G291" s="6">
-        <f t="shared" si="6"/>
-        <v>1121076360</v>
+      <c r="G291" s="1">
+        <v>0</v>
       </c>
       <c r="H291" s="1">
         <v>0</v>
       </c>
-      <c r="I291" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" s="6"/>
       <c r="B292" s="1">
         <v>94</v>
@@ -8631,18 +7479,14 @@
       <c r="F292" s="6">
         <v>120000000</v>
       </c>
-      <c r="G292" s="6">
-        <f t="shared" si="6"/>
-        <v>1241076360</v>
+      <c r="G292" s="1">
+        <v>0</v>
       </c>
       <c r="H292" s="1">
         <v>0</v>
       </c>
-      <c r="I292" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" s="6"/>
       <c r="B293" s="1">
         <v>95</v>
@@ -8659,18 +7503,14 @@
       <c r="F293" s="6">
         <v>130000000</v>
       </c>
-      <c r="G293" s="6">
-        <f t="shared" si="6"/>
-        <v>1371076360</v>
+      <c r="G293" s="1">
+        <v>0</v>
       </c>
       <c r="H293" s="1">
         <v>0</v>
       </c>
-      <c r="I293" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" s="6"/>
       <c r="B294" s="1">
         <v>96</v>
@@ -8687,18 +7527,14 @@
       <c r="F294" s="6">
         <v>150000000</v>
       </c>
-      <c r="G294" s="6">
-        <f t="shared" si="6"/>
-        <v>1521076360</v>
+      <c r="G294" s="1">
+        <v>0</v>
       </c>
       <c r="H294" s="1">
         <v>0</v>
       </c>
-      <c r="I294" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" s="6"/>
       <c r="B295" s="1">
         <v>97</v>
@@ -8715,18 +7551,14 @@
       <c r="F295" s="6">
         <v>150000000</v>
       </c>
-      <c r="G295" s="6">
-        <f t="shared" si="6"/>
-        <v>1671076360</v>
+      <c r="G295" s="1">
+        <v>0</v>
       </c>
       <c r="H295" s="1">
         <v>0</v>
       </c>
-      <c r="I295" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" s="6"/>
       <c r="B296" s="1">
         <v>98</v>
@@ -8743,18 +7575,14 @@
       <c r="F296" s="6">
         <v>300000000</v>
       </c>
-      <c r="G296" s="6">
-        <f t="shared" si="6"/>
-        <v>1971076360</v>
+      <c r="G296" s="1">
+        <v>0</v>
       </c>
       <c r="H296" s="1">
         <v>0</v>
       </c>
-      <c r="I296" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" s="6"/>
       <c r="B297" s="1">
         <v>99</v>
@@ -8771,20 +7599,16 @@
       <c r="F297" s="6">
         <v>0</v>
       </c>
-      <c r="G297" s="6">
-        <f t="shared" si="6"/>
-        <v>1971076360</v>
+      <c r="G297" s="1">
+        <v>0</v>
       </c>
       <c r="H297" s="1">
         <v>0</v>
       </c>
-      <c r="I297" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A298" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B298" s="6"/>
       <c r="C298" s="6"/>
@@ -8793,9 +7617,8 @@
       <c r="F298" s="6"/>
       <c r="G298" s="6"/>
       <c r="H298" s="6"/>
-      <c r="I298" s="6"/>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" s="6"/>
       <c r="B299" s="1">
         <v>5</v>
@@ -8812,18 +7635,14 @@
       <c r="F299" s="6">
         <v>1040</v>
       </c>
-      <c r="G299" s="6">
-        <f>SUM(G9,F299)</f>
-        <v>2240</v>
+      <c r="G299" s="1">
+        <v>0</v>
       </c>
       <c r="H299" s="1">
         <v>0</v>
       </c>
-      <c r="I299" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" s="6"/>
       <c r="B300" s="1">
         <v>6</v>
@@ -8840,18 +7659,14 @@
       <c r="F300" s="6">
         <v>1040</v>
       </c>
-      <c r="G300" s="6">
-        <f>SUM(G299,F300)</f>
-        <v>3280</v>
+      <c r="G300" s="1">
+        <v>0</v>
       </c>
       <c r="H300" s="1">
         <v>0</v>
       </c>
-      <c r="I300" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" s="6"/>
       <c r="B301" s="1">
         <v>7</v>
@@ -8868,18 +7683,14 @@
       <c r="F301" s="6">
         <v>1040</v>
       </c>
-      <c r="G301" s="6">
-        <f t="shared" ref="G301:G364" si="7">SUM(G300,F301)</f>
-        <v>4320</v>
+      <c r="G301" s="1">
+        <v>0</v>
       </c>
       <c r="H301" s="1">
         <v>0</v>
       </c>
-      <c r="I301" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" s="6"/>
       <c r="B302" s="1">
         <v>8</v>
@@ -8896,18 +7707,14 @@
       <c r="F302" s="6">
         <v>1800</v>
       </c>
-      <c r="G302" s="6">
-        <f t="shared" si="7"/>
-        <v>6120</v>
+      <c r="G302" s="1">
+        <v>0</v>
       </c>
       <c r="H302" s="1">
         <v>0</v>
       </c>
-      <c r="I302" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" s="6"/>
       <c r="B303" s="1">
         <v>9</v>
@@ -8924,18 +7731,14 @@
       <c r="F303" s="6">
         <v>1800</v>
       </c>
-      <c r="G303" s="6">
-        <f t="shared" si="7"/>
-        <v>7920</v>
+      <c r="G303" s="1">
+        <v>0</v>
       </c>
       <c r="H303" s="1">
         <v>0</v>
       </c>
-      <c r="I303" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" s="6"/>
       <c r="B304" s="1">
         <v>10</v>
@@ -8952,18 +7755,14 @@
       <c r="F304" s="6">
         <v>1800</v>
       </c>
-      <c r="G304" s="6">
-        <f t="shared" si="7"/>
-        <v>9720</v>
+      <c r="G304" s="1">
+        <v>0</v>
       </c>
       <c r="H304" s="1">
         <v>0</v>
       </c>
-      <c r="I304" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" s="6"/>
       <c r="B305" s="1">
         <v>11</v>
@@ -8980,18 +7779,14 @@
       <c r="F305" s="6">
         <v>1820</v>
       </c>
-      <c r="G305" s="6">
-        <f t="shared" si="7"/>
-        <v>11540</v>
+      <c r="G305" s="1">
+        <v>0</v>
       </c>
       <c r="H305" s="1">
         <v>0</v>
       </c>
-      <c r="I305" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" s="6"/>
       <c r="B306" s="1">
         <v>12</v>
@@ -9008,18 +7803,14 @@
       <c r="F306" s="6">
         <v>4320</v>
       </c>
-      <c r="G306" s="6">
-        <f t="shared" si="7"/>
-        <v>15860</v>
+      <c r="G306" s="1">
+        <v>0</v>
       </c>
       <c r="H306" s="1">
         <v>0</v>
       </c>
-      <c r="I306" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" s="6"/>
       <c r="B307" s="1">
         <v>13</v>
@@ -9036,18 +7827,14 @@
       <c r="F307" s="6">
         <v>4320</v>
       </c>
-      <c r="G307" s="6">
-        <f t="shared" si="7"/>
-        <v>20180</v>
+      <c r="G307" s="1">
+        <v>0</v>
       </c>
       <c r="H307" s="1">
         <v>0</v>
       </c>
-      <c r="I307" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" s="6"/>
       <c r="B308" s="1">
         <v>14</v>
@@ -9064,18 +7851,14 @@
       <c r="F308" s="6">
         <v>4320</v>
       </c>
-      <c r="G308" s="6">
-        <f t="shared" si="7"/>
-        <v>24500</v>
+      <c r="G308" s="1">
+        <v>0</v>
       </c>
       <c r="H308" s="1">
         <v>0</v>
       </c>
-      <c r="I308" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" s="6"/>
       <c r="B309" s="1">
         <v>15</v>
@@ -9092,18 +7875,14 @@
       <c r="F309" s="6">
         <v>8640</v>
       </c>
-      <c r="G309" s="6">
-        <f t="shared" si="7"/>
-        <v>33140</v>
+      <c r="G309" s="1">
+        <v>0</v>
       </c>
       <c r="H309" s="1">
         <v>0</v>
       </c>
-      <c r="I309" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" s="6"/>
       <c r="B310" s="1">
         <v>16</v>
@@ -9120,18 +7899,14 @@
       <c r="F310" s="6">
         <v>8640</v>
       </c>
-      <c r="G310" s="6">
-        <f t="shared" si="7"/>
-        <v>41780</v>
+      <c r="G310" s="1">
+        <v>0</v>
       </c>
       <c r="H310" s="1">
         <v>0</v>
       </c>
-      <c r="I310" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" s="6"/>
       <c r="B311" s="1">
         <v>17</v>
@@ -9148,18 +7923,14 @@
       <c r="F311" s="6">
         <v>8640</v>
       </c>
-      <c r="G311" s="6">
-        <f t="shared" si="7"/>
-        <v>50420</v>
+      <c r="G311" s="1">
+        <v>0</v>
       </c>
       <c r="H311" s="1">
         <v>0</v>
       </c>
-      <c r="I311" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" s="6"/>
       <c r="B312" s="1">
         <v>18</v>
@@ -9176,18 +7947,14 @@
       <c r="F312" s="6">
         <v>17280</v>
       </c>
-      <c r="G312" s="6">
-        <f t="shared" si="7"/>
-        <v>67700</v>
+      <c r="G312" s="1">
+        <v>0</v>
       </c>
       <c r="H312" s="1">
         <v>0</v>
       </c>
-      <c r="I312" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" s="6"/>
       <c r="B313" s="1">
         <v>19</v>
@@ -9204,18 +7971,14 @@
       <c r="F313" s="6">
         <v>17280</v>
       </c>
-      <c r="G313" s="6">
-        <f t="shared" si="7"/>
-        <v>84980</v>
+      <c r="G313" s="1">
+        <v>0</v>
       </c>
       <c r="H313" s="1">
         <v>0</v>
       </c>
-      <c r="I313" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" s="6"/>
       <c r="B314" s="1">
         <v>20</v>
@@ -9232,18 +7995,14 @@
       <c r="F314" s="6">
         <v>17280</v>
       </c>
-      <c r="G314" s="6">
-        <f t="shared" si="7"/>
-        <v>102260</v>
+      <c r="G314" s="1">
+        <v>0</v>
       </c>
       <c r="H314" s="1">
         <v>0</v>
       </c>
-      <c r="I314" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" s="6"/>
       <c r="B315" s="1">
         <v>21</v>
@@ -9260,18 +8019,14 @@
       <c r="F315" s="6">
         <v>34000</v>
       </c>
-      <c r="G315" s="6">
-        <f t="shared" si="7"/>
-        <v>136260</v>
+      <c r="G315" s="1">
+        <v>0</v>
       </c>
       <c r="H315" s="1">
         <v>0</v>
       </c>
-      <c r="I315" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" s="6"/>
       <c r="B316" s="1">
         <v>22</v>
@@ -9288,18 +8043,14 @@
       <c r="F316" s="6">
         <v>34000</v>
       </c>
-      <c r="G316" s="6">
-        <f t="shared" si="7"/>
-        <v>170260</v>
+      <c r="G316" s="1">
+        <v>0</v>
       </c>
       <c r="H316" s="1">
         <v>0</v>
       </c>
-      <c r="I316" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" s="6"/>
       <c r="B317" s="1">
         <v>23</v>
@@ -9316,18 +8067,14 @@
       <c r="F317" s="6">
         <v>34000</v>
       </c>
-      <c r="G317" s="6">
-        <f t="shared" si="7"/>
-        <v>204260</v>
+      <c r="G317" s="1">
+        <v>0</v>
       </c>
       <c r="H317" s="1">
         <v>0</v>
       </c>
-      <c r="I317" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" s="6"/>
       <c r="B318" s="1">
         <v>24</v>
@@ -9344,18 +8091,14 @@
       <c r="F318" s="6">
         <v>69000</v>
       </c>
-      <c r="G318" s="6">
-        <f t="shared" si="7"/>
-        <v>273260</v>
+      <c r="G318" s="1">
+        <v>0</v>
       </c>
       <c r="H318" s="1">
         <v>0</v>
       </c>
-      <c r="I318" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" s="6"/>
       <c r="B319" s="1">
         <v>25</v>
@@ -9372,18 +8115,14 @@
       <c r="F319" s="6">
         <v>69000</v>
       </c>
-      <c r="G319" s="6">
-        <f t="shared" si="7"/>
-        <v>342260</v>
+      <c r="G319" s="1">
+        <v>0</v>
       </c>
       <c r="H319" s="1">
         <v>0</v>
       </c>
-      <c r="I319" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" s="6"/>
       <c r="B320" s="1">
         <v>26</v>
@@ -9400,18 +8139,14 @@
       <c r="F320" s="6">
         <v>69000</v>
       </c>
-      <c r="G320" s="6">
-        <f t="shared" si="7"/>
-        <v>411260</v>
+      <c r="G320" s="1">
+        <v>0</v>
       </c>
       <c r="H320" s="1">
         <v>0</v>
       </c>
-      <c r="I320" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" s="6"/>
       <c r="B321" s="1">
         <v>27</v>
@@ -9428,18 +8163,14 @@
       <c r="F321" s="6">
         <v>140000</v>
       </c>
-      <c r="G321" s="6">
-        <f t="shared" si="7"/>
-        <v>551260</v>
+      <c r="G321" s="1">
+        <v>0</v>
       </c>
       <c r="H321" s="1">
         <v>0</v>
       </c>
-      <c r="I321" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" s="6"/>
       <c r="B322" s="1">
         <v>28</v>
@@ -9456,18 +8187,14 @@
       <c r="F322" s="6">
         <v>140000</v>
       </c>
-      <c r="G322" s="6">
-        <f t="shared" si="7"/>
-        <v>691260</v>
+      <c r="G322" s="1">
+        <v>0</v>
       </c>
       <c r="H322" s="1">
         <v>0</v>
       </c>
-      <c r="I322" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" s="6"/>
       <c r="B323" s="1">
         <v>29</v>
@@ -9484,18 +8211,14 @@
       <c r="F323" s="6">
         <v>140000</v>
       </c>
-      <c r="G323" s="6">
-        <f t="shared" si="7"/>
-        <v>831260</v>
+      <c r="G323" s="1">
+        <v>0</v>
       </c>
       <c r="H323" s="1">
         <v>0</v>
       </c>
-      <c r="I323" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" s="6"/>
       <c r="B324" s="1">
         <v>30</v>
@@ -9512,18 +8235,14 @@
       <c r="F324" s="6">
         <v>180000</v>
       </c>
-      <c r="G324" s="6">
-        <f t="shared" si="7"/>
-        <v>1011260</v>
+      <c r="G324" s="1">
+        <v>0</v>
       </c>
       <c r="H324" s="1">
         <v>0</v>
       </c>
-      <c r="I324" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" s="6"/>
       <c r="B325" s="1">
         <v>31</v>
@@ -9540,18 +8259,14 @@
       <c r="F325" s="6">
         <v>180000</v>
       </c>
-      <c r="G325" s="6">
-        <f t="shared" si="7"/>
-        <v>1191260</v>
+      <c r="G325" s="1">
+        <v>0</v>
       </c>
       <c r="H325" s="1">
         <v>0</v>
       </c>
-      <c r="I325" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A326" s="6"/>
       <c r="B326" s="1">
         <v>32</v>
@@ -9568,18 +8283,14 @@
       <c r="F326" s="6">
         <v>180000</v>
       </c>
-      <c r="G326" s="6">
-        <f t="shared" si="7"/>
-        <v>1371260</v>
+      <c r="G326" s="1">
+        <v>0</v>
       </c>
       <c r="H326" s="1">
         <v>0</v>
       </c>
-      <c r="I326" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" s="6"/>
       <c r="B327" s="1">
         <v>33</v>
@@ -9596,18 +8307,14 @@
       <c r="F327" s="6">
         <v>290000</v>
       </c>
-      <c r="G327" s="6">
-        <f t="shared" si="7"/>
-        <v>1661260</v>
+      <c r="G327" s="1">
+        <v>0</v>
       </c>
       <c r="H327" s="1">
         <v>0</v>
       </c>
-      <c r="I327" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" s="6"/>
       <c r="B328" s="1">
         <v>34</v>
@@ -9624,18 +8331,14 @@
       <c r="F328" s="6">
         <v>290000</v>
       </c>
-      <c r="G328" s="6">
-        <f t="shared" si="7"/>
-        <v>1951260</v>
+      <c r="G328" s="1">
+        <v>0</v>
       </c>
       <c r="H328" s="1">
         <v>0</v>
       </c>
-      <c r="I328" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" s="6"/>
       <c r="B329" s="1">
         <v>35</v>
@@ -9652,18 +8355,14 @@
       <c r="F329" s="6">
         <v>290000</v>
       </c>
-      <c r="G329" s="6">
-        <f t="shared" si="7"/>
-        <v>2241260</v>
+      <c r="G329" s="1">
+        <v>0</v>
       </c>
       <c r="H329" s="1">
         <v>0</v>
       </c>
-      <c r="I329" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" s="6"/>
       <c r="B330" s="1">
         <v>36</v>
@@ -9680,18 +8379,14 @@
       <c r="F330" s="6">
         <v>410000</v>
       </c>
-      <c r="G330" s="6">
-        <f t="shared" si="7"/>
-        <v>2651260</v>
+      <c r="G330" s="1">
+        <v>0</v>
       </c>
       <c r="H330" s="1">
         <v>0</v>
       </c>
-      <c r="I330" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" s="6"/>
       <c r="B331" s="1">
         <v>37</v>
@@ -9708,18 +8403,14 @@
       <c r="F331" s="6">
         <v>410000</v>
       </c>
-      <c r="G331" s="6">
-        <f t="shared" si="7"/>
-        <v>3061260</v>
+      <c r="G331" s="1">
+        <v>0</v>
       </c>
       <c r="H331" s="1">
         <v>0</v>
       </c>
-      <c r="I331" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" s="6"/>
       <c r="B332" s="1">
         <v>38</v>
@@ -9736,18 +8427,14 @@
       <c r="F332" s="6">
         <v>410000</v>
       </c>
-      <c r="G332" s="6">
-        <f t="shared" si="7"/>
-        <v>3471260</v>
+      <c r="G332" s="1">
+        <v>0</v>
       </c>
       <c r="H332" s="1">
         <v>0</v>
       </c>
-      <c r="I332" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" s="6"/>
       <c r="B333" s="1">
         <v>39</v>
@@ -9764,18 +8451,14 @@
       <c r="F333" s="6">
         <v>440000</v>
       </c>
-      <c r="G333" s="6">
-        <f t="shared" si="7"/>
-        <v>3911260</v>
+      <c r="G333" s="1">
+        <v>0</v>
       </c>
       <c r="H333" s="1">
         <v>0</v>
       </c>
-      <c r="I333" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" s="6"/>
       <c r="B334" s="1">
         <v>40</v>
@@ -9792,18 +8475,14 @@
       <c r="F334" s="6">
         <v>440000</v>
       </c>
-      <c r="G334" s="6">
-        <f t="shared" si="7"/>
-        <v>4351260</v>
+      <c r="G334" s="1">
+        <v>0</v>
       </c>
       <c r="H334" s="1">
         <v>0</v>
       </c>
-      <c r="I334" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" s="6"/>
       <c r="B335" s="1">
         <v>41</v>
@@ -9820,18 +8499,14 @@
       <c r="F335" s="6">
         <v>440000</v>
       </c>
-      <c r="G335" s="6">
-        <f t="shared" si="7"/>
-        <v>4791260</v>
+      <c r="G335" s="1">
+        <v>0</v>
       </c>
       <c r="H335" s="1">
         <v>0</v>
       </c>
-      <c r="I335" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" s="6"/>
       <c r="B336" s="1">
         <v>42</v>
@@ -9848,18 +8523,14 @@
       <c r="F336" s="6">
         <v>640000</v>
       </c>
-      <c r="G336" s="6">
-        <f t="shared" si="7"/>
-        <v>5431260</v>
+      <c r="G336" s="1">
+        <v>0</v>
       </c>
       <c r="H336" s="1">
         <v>0</v>
       </c>
-      <c r="I336" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A337" s="6"/>
       <c r="B337" s="1">
         <v>43</v>
@@ -9876,18 +8547,14 @@
       <c r="F337" s="6">
         <v>640000</v>
       </c>
-      <c r="G337" s="6">
-        <f t="shared" si="7"/>
-        <v>6071260</v>
+      <c r="G337" s="1">
+        <v>0</v>
       </c>
       <c r="H337" s="1">
         <v>0</v>
       </c>
-      <c r="I337" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A338" s="6"/>
       <c r="B338" s="1">
         <v>44</v>
@@ -9904,18 +8571,14 @@
       <c r="F338" s="6">
         <v>640000</v>
       </c>
-      <c r="G338" s="6">
-        <f t="shared" si="7"/>
-        <v>6711260</v>
+      <c r="G338" s="1">
+        <v>0</v>
       </c>
       <c r="H338" s="1">
         <v>0</v>
       </c>
-      <c r="I338" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A339" s="6"/>
       <c r="B339" s="1">
         <v>45</v>
@@ -9932,18 +8595,14 @@
       <c r="F339" s="6">
         <v>880000</v>
       </c>
-      <c r="G339" s="6">
-        <f t="shared" si="7"/>
-        <v>7591260</v>
+      <c r="G339" s="1">
+        <v>0</v>
       </c>
       <c r="H339" s="1">
         <v>0</v>
       </c>
-      <c r="I339" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A340" s="6"/>
       <c r="B340" s="1">
         <v>46</v>
@@ -9960,18 +8619,14 @@
       <c r="F340" s="6">
         <v>880000</v>
       </c>
-      <c r="G340" s="6">
-        <f t="shared" si="7"/>
-        <v>8471260</v>
+      <c r="G340" s="1">
+        <v>0</v>
       </c>
       <c r="H340" s="1">
         <v>0</v>
       </c>
-      <c r="I340" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A341" s="6"/>
       <c r="B341" s="1">
         <v>47</v>
@@ -9988,18 +8643,14 @@
       <c r="F341" s="6">
         <v>880000</v>
       </c>
-      <c r="G341" s="6">
-        <f t="shared" si="7"/>
-        <v>9351260</v>
+      <c r="G341" s="1">
+        <v>0</v>
       </c>
       <c r="H341" s="1">
         <v>0</v>
       </c>
-      <c r="I341" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A342" s="6"/>
       <c r="B342" s="1">
         <v>48</v>
@@ -10016,18 +8667,14 @@
       <c r="F342" s="6">
         <v>1300000</v>
       </c>
-      <c r="G342" s="6">
-        <f t="shared" si="7"/>
-        <v>10651260</v>
+      <c r="G342" s="1">
+        <v>0</v>
       </c>
       <c r="H342" s="1">
         <v>0</v>
       </c>
-      <c r="I342" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A343" s="6"/>
       <c r="B343" s="1">
         <v>49</v>
@@ -10044,18 +8691,14 @@
       <c r="F343" s="6">
         <v>1300000</v>
       </c>
-      <c r="G343" s="6">
-        <f t="shared" si="7"/>
-        <v>11951260</v>
+      <c r="G343" s="1">
+        <v>0</v>
       </c>
       <c r="H343" s="1">
         <v>0</v>
       </c>
-      <c r="I343" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A344" s="6"/>
       <c r="B344" s="1">
         <v>50</v>
@@ -10072,18 +8715,14 @@
       <c r="F344" s="6">
         <v>1300000</v>
       </c>
-      <c r="G344" s="6">
-        <f t="shared" si="7"/>
-        <v>13251260</v>
+      <c r="G344" s="1">
+        <v>0</v>
       </c>
       <c r="H344" s="1">
         <v>0</v>
       </c>
-      <c r="I344" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A345" s="6"/>
       <c r="B345" s="1">
         <v>51</v>
@@ -10100,18 +8739,14 @@
       <c r="F345" s="6">
         <v>1500000</v>
       </c>
-      <c r="G345" s="6">
-        <f t="shared" si="7"/>
-        <v>14751260</v>
+      <c r="G345" s="1">
+        <v>0</v>
       </c>
       <c r="H345" s="1">
         <v>0</v>
       </c>
-      <c r="I345" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A346" s="6"/>
       <c r="B346" s="1">
         <v>52</v>
@@ -10128,18 +8763,14 @@
       <c r="F346" s="6">
         <v>1500000</v>
       </c>
-      <c r="G346" s="6">
-        <f t="shared" si="7"/>
-        <v>16251260</v>
+      <c r="G346" s="1">
+        <v>0</v>
       </c>
       <c r="H346" s="1">
         <v>0</v>
       </c>
-      <c r="I346" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A347" s="6"/>
       <c r="B347" s="1">
         <v>53</v>
@@ -10156,18 +8787,14 @@
       <c r="F347" s="6">
         <v>1500000</v>
       </c>
-      <c r="G347" s="6">
-        <f t="shared" si="7"/>
-        <v>17751260</v>
+      <c r="G347" s="1">
+        <v>0</v>
       </c>
       <c r="H347" s="1">
         <v>0</v>
       </c>
-      <c r="I347" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A348" s="6"/>
       <c r="B348" s="1">
         <v>54</v>
@@ -10184,18 +8811,14 @@
       <c r="F348" s="6">
         <v>2160000</v>
       </c>
-      <c r="G348" s="6">
-        <f t="shared" si="7"/>
-        <v>19911260</v>
+      <c r="G348" s="1">
+        <v>0</v>
       </c>
       <c r="H348" s="1">
         <v>0</v>
       </c>
-      <c r="I348" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A349" s="6"/>
       <c r="B349" s="1">
         <v>55</v>
@@ -10212,18 +8835,14 @@
       <c r="F349" s="6">
         <v>2160000</v>
       </c>
-      <c r="G349" s="6">
-        <f t="shared" si="7"/>
-        <v>22071260</v>
+      <c r="G349" s="1">
+        <v>0</v>
       </c>
       <c r="H349" s="1">
         <v>0</v>
       </c>
-      <c r="I349" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A350" s="6"/>
       <c r="B350" s="1">
         <v>56</v>
@@ -10240,18 +8859,14 @@
       <c r="F350" s="6">
         <v>2160000</v>
       </c>
-      <c r="G350" s="6">
-        <f t="shared" si="7"/>
-        <v>24231260</v>
+      <c r="G350" s="1">
+        <v>0</v>
       </c>
       <c r="H350" s="1">
         <v>0</v>
       </c>
-      <c r="I350" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A351" s="6"/>
       <c r="B351" s="1">
         <v>57</v>
@@ -10268,18 +8883,14 @@
       <c r="F351" s="6">
         <v>3340000</v>
       </c>
-      <c r="G351" s="6">
-        <f t="shared" si="7"/>
-        <v>27571260</v>
+      <c r="G351" s="1">
+        <v>0</v>
       </c>
       <c r="H351" s="1">
         <v>0</v>
       </c>
-      <c r="I351" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A352" s="6"/>
       <c r="B352" s="1">
         <v>58</v>
@@ -10296,18 +8907,14 @@
       <c r="F352" s="6">
         <v>4850000</v>
       </c>
-      <c r="G352" s="6">
-        <f t="shared" si="7"/>
-        <v>32421260</v>
+      <c r="G352" s="1">
+        <v>0</v>
       </c>
       <c r="H352" s="1">
         <v>0</v>
       </c>
-      <c r="I352" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A353" s="6"/>
       <c r="B353" s="1">
         <v>59</v>
@@ -10324,18 +8931,14 @@
       <c r="F353" s="6">
         <v>4350000</v>
       </c>
-      <c r="G353" s="6">
-        <f t="shared" si="7"/>
-        <v>36771260</v>
+      <c r="G353" s="1">
+        <v>0</v>
       </c>
       <c r="H353" s="1">
         <v>0</v>
       </c>
-      <c r="I353" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A354" s="6"/>
       <c r="B354" s="1">
         <v>60</v>
@@ -10352,18 +8955,14 @@
       <c r="F354" s="6">
         <v>6900000</v>
       </c>
-      <c r="G354" s="6">
-        <f t="shared" si="7"/>
-        <v>43671260</v>
+      <c r="G354" s="1">
+        <v>0</v>
       </c>
       <c r="H354" s="1">
         <v>0</v>
       </c>
-      <c r="I354" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A355" s="6"/>
       <c r="B355" s="1">
         <v>61</v>
@@ -10380,18 +8979,14 @@
       <c r="F355" s="6">
         <v>6900000</v>
       </c>
-      <c r="G355" s="6">
-        <f t="shared" si="7"/>
-        <v>50571260</v>
+      <c r="G355" s="1">
+        <v>0</v>
       </c>
       <c r="H355" s="1">
         <v>0</v>
       </c>
-      <c r="I355" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A356" s="6"/>
       <c r="B356" s="1">
         <v>62</v>
@@ -10408,18 +9003,14 @@
       <c r="F356" s="6">
         <v>6900000</v>
       </c>
-      <c r="G356" s="6">
-        <f t="shared" si="7"/>
-        <v>57471260</v>
+      <c r="G356" s="1">
+        <v>0</v>
       </c>
       <c r="H356" s="1">
         <v>0</v>
       </c>
-      <c r="I356" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A357" s="6"/>
       <c r="B357" s="1">
         <v>63</v>
@@ -10436,18 +9027,14 @@
       <c r="F357" s="6">
         <v>8000000</v>
       </c>
-      <c r="G357" s="6">
-        <f t="shared" si="7"/>
-        <v>65471260</v>
+      <c r="G357" s="1">
+        <v>0</v>
       </c>
       <c r="H357" s="1">
         <v>0</v>
       </c>
-      <c r="I357" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A358" s="6"/>
       <c r="B358" s="1">
         <v>64</v>
@@ -10464,18 +9051,14 @@
       <c r="F358" s="6">
         <v>8000000</v>
       </c>
-      <c r="G358" s="6">
-        <f t="shared" si="7"/>
-        <v>73471260</v>
+      <c r="G358" s="1">
+        <v>0</v>
       </c>
       <c r="H358" s="1">
         <v>0</v>
       </c>
-      <c r="I358" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A359" s="6"/>
       <c r="B359" s="1">
         <v>65</v>
@@ -10492,18 +9075,14 @@
       <c r="F359" s="6">
         <v>8000000</v>
       </c>
-      <c r="G359" s="6">
-        <f t="shared" si="7"/>
-        <v>81471260</v>
+      <c r="G359" s="1">
+        <v>0</v>
       </c>
       <c r="H359" s="1">
         <v>0</v>
       </c>
-      <c r="I359" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A360" s="6"/>
       <c r="B360" s="1">
         <v>66</v>
@@ -10520,18 +9099,14 @@
       <c r="F360" s="6">
         <v>10000000</v>
       </c>
-      <c r="G360" s="6">
-        <f t="shared" si="7"/>
-        <v>91471260</v>
+      <c r="G360" s="1">
+        <v>0</v>
       </c>
       <c r="H360" s="1">
         <v>0</v>
       </c>
-      <c r="I360" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A361" s="6"/>
       <c r="B361" s="1">
         <v>67</v>
@@ -10548,18 +9123,14 @@
       <c r="F361" s="6">
         <v>9000000</v>
       </c>
-      <c r="G361" s="6">
-        <f t="shared" si="7"/>
-        <v>100471260</v>
+      <c r="G361" s="1">
+        <v>0</v>
       </c>
       <c r="H361" s="1">
         <v>0</v>
       </c>
-      <c r="I361" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A362" s="6"/>
       <c r="B362" s="1">
         <v>68</v>
@@ -10576,18 +9147,14 @@
       <c r="F362" s="6">
         <v>10000000</v>
       </c>
-      <c r="G362" s="6">
-        <f t="shared" si="7"/>
-        <v>110471260</v>
+      <c r="G362" s="1">
+        <v>0</v>
       </c>
       <c r="H362" s="1">
         <v>0</v>
       </c>
-      <c r="I362" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A363" s="6"/>
       <c r="B363" s="1">
         <v>69</v>
@@ -10604,18 +9171,14 @@
       <c r="F363" s="6">
         <v>10000000</v>
       </c>
-      <c r="G363" s="6">
-        <f t="shared" si="7"/>
-        <v>120471260</v>
+      <c r="G363" s="1">
+        <v>0</v>
       </c>
       <c r="H363" s="1">
         <v>0</v>
       </c>
-      <c r="I363" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A364" s="6"/>
       <c r="B364" s="1">
         <v>70</v>
@@ -10632,18 +9195,14 @@
       <c r="F364" s="6">
         <v>10000000</v>
       </c>
-      <c r="G364" s="6">
-        <f t="shared" si="7"/>
-        <v>130471260</v>
+      <c r="G364" s="1">
+        <v>0</v>
       </c>
       <c r="H364" s="1">
         <v>0</v>
       </c>
-      <c r="I364" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A365" s="6"/>
       <c r="B365" s="1">
         <v>71</v>
@@ -10660,18 +9219,14 @@
       <c r="F365" s="6">
         <v>20000000</v>
       </c>
-      <c r="G365" s="6">
-        <f t="shared" ref="G365:G393" si="8">SUM(G364,F365)</f>
-        <v>150471260</v>
+      <c r="G365" s="1">
+        <v>0</v>
       </c>
       <c r="H365" s="1">
         <v>0</v>
       </c>
-      <c r="I365" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A366" s="6"/>
       <c r="B366" s="1">
         <v>72</v>
@@ -10688,18 +9243,14 @@
       <c r="F366" s="6">
         <v>20000000</v>
       </c>
-      <c r="G366" s="6">
-        <f t="shared" si="8"/>
-        <v>170471260</v>
+      <c r="G366" s="1">
+        <v>0</v>
       </c>
       <c r="H366" s="1">
         <v>0</v>
       </c>
-      <c r="I366" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A367" s="6"/>
       <c r="B367" s="1">
         <v>73</v>
@@ -10716,18 +9267,14 @@
       <c r="F367" s="6">
         <v>20000000</v>
       </c>
-      <c r="G367" s="6">
-        <f t="shared" si="8"/>
-        <v>190471260</v>
+      <c r="G367" s="1">
+        <v>0</v>
       </c>
       <c r="H367" s="1">
         <v>0</v>
       </c>
-      <c r="I367" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A368" s="6"/>
       <c r="B368" s="1">
         <v>74</v>
@@ -10744,18 +9291,14 @@
       <c r="F368" s="6">
         <v>20000000</v>
       </c>
-      <c r="G368" s="6">
-        <f t="shared" si="8"/>
-        <v>210471260</v>
+      <c r="G368" s="1">
+        <v>0</v>
       </c>
       <c r="H368" s="1">
         <v>0</v>
       </c>
-      <c r="I368" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" s="6"/>
       <c r="B369" s="1">
         <v>75</v>
@@ -10772,18 +9315,14 @@
       <c r="F369" s="6">
         <v>30000000</v>
       </c>
-      <c r="G369" s="6">
-        <f t="shared" si="8"/>
-        <v>240471260</v>
+      <c r="G369" s="1">
+        <v>0</v>
       </c>
       <c r="H369" s="1">
         <v>0</v>
       </c>
-      <c r="I369" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" s="6"/>
       <c r="B370" s="1">
         <v>76</v>
@@ -10800,18 +9339,14 @@
       <c r="F370" s="6">
         <v>30000000</v>
       </c>
-      <c r="G370" s="6">
-        <f t="shared" si="8"/>
-        <v>270471260</v>
+      <c r="G370" s="1">
+        <v>0</v>
       </c>
       <c r="H370" s="1">
         <v>0</v>
       </c>
-      <c r="I370" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" s="6"/>
       <c r="B371" s="1">
         <v>77</v>
@@ -10828,18 +9363,14 @@
       <c r="F371" s="6">
         <v>30000000</v>
       </c>
-      <c r="G371" s="6">
-        <f t="shared" si="8"/>
-        <v>300471260</v>
+      <c r="G371" s="1">
+        <v>0</v>
       </c>
       <c r="H371" s="1">
         <v>0</v>
       </c>
-      <c r="I371" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" s="6"/>
       <c r="B372" s="1">
         <v>78</v>
@@ -10856,18 +9387,14 @@
       <c r="F372" s="6">
         <v>40000000</v>
       </c>
-      <c r="G372" s="6">
-        <f t="shared" si="8"/>
-        <v>340471260</v>
+      <c r="G372" s="1">
+        <v>0</v>
       </c>
       <c r="H372" s="1">
         <v>0</v>
       </c>
-      <c r="I372" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" s="6"/>
       <c r="B373" s="1">
         <v>79</v>
@@ -10884,18 +9411,14 @@
       <c r="F373" s="6">
         <v>40000000</v>
       </c>
-      <c r="G373" s="6">
-        <f t="shared" si="8"/>
-        <v>380471260</v>
+      <c r="G373" s="1">
+        <v>0</v>
       </c>
       <c r="H373" s="1">
         <v>0</v>
       </c>
-      <c r="I373" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" s="6"/>
       <c r="B374" s="1">
         <v>80</v>
@@ -10912,18 +9435,14 @@
       <c r="F374" s="6">
         <v>40000000</v>
       </c>
-      <c r="G374" s="6">
-        <f t="shared" si="8"/>
-        <v>420471260</v>
+      <c r="G374" s="1">
+        <v>0</v>
       </c>
       <c r="H374" s="1">
         <v>0</v>
       </c>
-      <c r="I374" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" s="6"/>
       <c r="B375" s="1">
         <v>81</v>
@@ -10940,18 +9459,14 @@
       <c r="F375" s="6">
         <v>50000000</v>
       </c>
-      <c r="G375" s="6">
-        <f t="shared" si="8"/>
-        <v>470471260</v>
+      <c r="G375" s="1">
+        <v>0</v>
       </c>
       <c r="H375" s="1">
         <v>0</v>
       </c>
-      <c r="I375" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" s="6"/>
       <c r="B376" s="1">
         <v>82</v>
@@ -10968,18 +9483,14 @@
       <c r="F376" s="6">
         <v>50000000</v>
       </c>
-      <c r="G376" s="6">
-        <f t="shared" si="8"/>
-        <v>520471260</v>
+      <c r="G376" s="1">
+        <v>0</v>
       </c>
       <c r="H376" s="1">
         <v>0</v>
       </c>
-      <c r="I376" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" s="6"/>
       <c r="B377" s="1">
         <v>83</v>
@@ -10996,18 +9507,14 @@
       <c r="F377" s="6">
         <v>60000000</v>
       </c>
-      <c r="G377" s="6">
-        <f t="shared" si="8"/>
-        <v>580471260</v>
+      <c r="G377" s="1">
+        <v>0</v>
       </c>
       <c r="H377" s="1">
         <v>0</v>
       </c>
-      <c r="I377" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" s="6"/>
       <c r="B378" s="1">
         <v>84</v>
@@ -11024,18 +9531,14 @@
       <c r="F378" s="6">
         <v>60000000</v>
       </c>
-      <c r="G378" s="6">
-        <f t="shared" si="8"/>
-        <v>640471260</v>
+      <c r="G378" s="1">
+        <v>0</v>
       </c>
       <c r="H378" s="1">
         <v>0</v>
       </c>
-      <c r="I378" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" s="6"/>
       <c r="B379" s="1">
         <v>85</v>
@@ -11052,18 +9555,14 @@
       <c r="F379" s="6">
         <v>70000000</v>
       </c>
-      <c r="G379" s="6">
-        <f t="shared" si="8"/>
-        <v>710471260</v>
+      <c r="G379" s="1">
+        <v>0</v>
       </c>
       <c r="H379" s="1">
         <v>0</v>
       </c>
-      <c r="I379" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A380" s="6"/>
       <c r="B380" s="1">
         <v>86</v>
@@ -11080,18 +9579,14 @@
       <c r="F380" s="6">
         <v>80000000</v>
       </c>
-      <c r="G380" s="6">
-        <f t="shared" si="8"/>
-        <v>790471260</v>
+      <c r="G380" s="1">
+        <v>0</v>
       </c>
       <c r="H380" s="1">
         <v>0</v>
       </c>
-      <c r="I380" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A381" s="6"/>
       <c r="B381" s="1">
         <v>87</v>
@@ -11108,18 +9603,14 @@
       <c r="F381" s="6">
         <v>90000000</v>
       </c>
-      <c r="G381" s="6">
-        <f t="shared" si="8"/>
-        <v>880471260</v>
+      <c r="G381" s="1">
+        <v>0</v>
       </c>
       <c r="H381" s="1">
         <v>0</v>
       </c>
-      <c r="I381" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" s="6"/>
       <c r="B382" s="1">
         <v>88</v>
@@ -11136,18 +9627,14 @@
       <c r="F382" s="6">
         <v>100000000</v>
       </c>
-      <c r="G382" s="6">
-        <f t="shared" si="8"/>
-        <v>980471260</v>
+      <c r="G382" s="1">
+        <v>0</v>
       </c>
       <c r="H382" s="1">
         <v>0</v>
       </c>
-      <c r="I382" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383" s="6"/>
       <c r="B383" s="1">
         <v>89</v>
@@ -11164,18 +9651,14 @@
       <c r="F383" s="6">
         <v>100000000</v>
       </c>
-      <c r="G383" s="6">
-        <f t="shared" si="8"/>
-        <v>1080471260</v>
+      <c r="G383" s="1">
+        <v>0</v>
       </c>
       <c r="H383" s="1">
         <v>0</v>
       </c>
-      <c r="I383" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" s="6"/>
       <c r="B384" s="1">
         <v>90</v>
@@ -11192,18 +9675,14 @@
       <c r="F384" s="6">
         <v>110000000</v>
       </c>
-      <c r="G384" s="6">
-        <f t="shared" si="8"/>
-        <v>1190471260</v>
+      <c r="G384" s="1">
+        <v>0</v>
       </c>
       <c r="H384" s="1">
         <v>0</v>
       </c>
-      <c r="I384" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" s="6"/>
       <c r="B385" s="1">
         <v>91</v>
@@ -11220,18 +9699,14 @@
       <c r="F385" s="6">
         <v>200000000</v>
       </c>
-      <c r="G385" s="6">
-        <f t="shared" si="8"/>
-        <v>1390471260</v>
+      <c r="G385" s="1">
+        <v>0</v>
       </c>
       <c r="H385" s="1">
         <v>0</v>
       </c>
-      <c r="I385" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" s="6"/>
       <c r="B386" s="1">
         <v>92</v>
@@ -11248,18 +9723,14 @@
       <c r="F386" s="6">
         <v>130000000</v>
       </c>
-      <c r="G386" s="6">
-        <f t="shared" si="8"/>
-        <v>1520471260</v>
+      <c r="G386" s="1">
+        <v>0</v>
       </c>
       <c r="H386" s="1">
         <v>0</v>
       </c>
-      <c r="I386" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" s="6"/>
       <c r="B387" s="1">
         <v>93</v>
@@ -11276,18 +9747,14 @@
       <c r="F387" s="6">
         <v>130000000</v>
       </c>
-      <c r="G387" s="6">
-        <f t="shared" si="8"/>
-        <v>1650471260</v>
+      <c r="G387" s="1">
+        <v>0</v>
       </c>
       <c r="H387" s="1">
         <v>0</v>
       </c>
-      <c r="I387" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" s="6"/>
       <c r="B388" s="1">
         <v>94</v>
@@ -11304,18 +9771,14 @@
       <c r="F388" s="6">
         <v>140000000</v>
       </c>
-      <c r="G388" s="6">
-        <f t="shared" si="8"/>
-        <v>1790471260</v>
+      <c r="G388" s="1">
+        <v>0</v>
       </c>
       <c r="H388" s="1">
         <v>0</v>
       </c>
-      <c r="I388" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" s="6"/>
       <c r="B389" s="1">
         <v>95</v>
@@ -11332,18 +9795,14 @@
       <c r="F389" s="6">
         <v>40000000</v>
       </c>
-      <c r="G389" s="6">
-        <f t="shared" si="8"/>
-        <v>1830471260</v>
+      <c r="G389" s="1">
+        <v>0</v>
       </c>
       <c r="H389" s="1">
         <v>0</v>
       </c>
-      <c r="I389" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" s="6"/>
       <c r="B390" s="1">
         <v>96</v>
@@ -11360,18 +9819,14 @@
       <c r="F390" s="6">
         <v>150000000</v>
       </c>
-      <c r="G390" s="6">
-        <f t="shared" si="8"/>
-        <v>1980471260</v>
+      <c r="G390" s="1">
+        <v>0</v>
       </c>
       <c r="H390" s="1">
         <v>0</v>
       </c>
-      <c r="I390" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" s="6"/>
       <c r="B391" s="1">
         <v>97</v>
@@ -11388,18 +9843,14 @@
       <c r="F391" s="6">
         <v>150000000</v>
       </c>
-      <c r="G391" s="6">
-        <f t="shared" si="8"/>
-        <v>2130471260</v>
+      <c r="G391" s="1">
+        <v>0</v>
       </c>
       <c r="H391" s="1">
         <v>0</v>
       </c>
-      <c r="I391" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" s="6"/>
       <c r="B392" s="1">
         <v>98</v>
@@ -11416,18 +9867,14 @@
       <c r="F392" s="6">
         <v>170000000</v>
       </c>
-      <c r="G392" s="6">
-        <f t="shared" si="8"/>
-        <v>2300471260</v>
+      <c r="G392" s="1">
+        <v>0</v>
       </c>
       <c r="H392" s="1">
         <v>0</v>
       </c>
-      <c r="I392" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" s="6"/>
       <c r="B393" s="1">
         <v>99</v>
@@ -11444,14 +9891,10 @@
       <c r="F393" s="6">
         <v>0</v>
       </c>
-      <c r="G393" s="6">
-        <f t="shared" si="8"/>
-        <v>2300471260</v>
+      <c r="G393" s="1">
+        <v>0</v>
       </c>
       <c r="H393" s="1">
-        <v>0</v>
-      </c>
-      <c r="I393" s="1">
         <v>0</v>
       </c>
     </row>
@@ -11504,7 +9947,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -11566,7 +10009,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -11598,7 +10041,7 @@
         <v>3</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -11611,7 +10054,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -11656,7 +10099,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
